--- a/database/event/3701/event_3701_evp_summary.xlsx
+++ b/database/event/3701/event_3701_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3836</v>
+        <v>6.58</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8545</v>
+        <v>2.2666</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7535</v>
+        <v>2.1776</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3836</v>
+        <v>6.58</v>
       </c>
       <c r="F2" t="n">
-        <v>3.6748</v>
+        <v>4.8712</v>
       </c>
       <c r="G2" t="n">
         <v>1.7088</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6748</v>
+        <v>5.335</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6919</v>
+        <v>5.3799</v>
       </c>
       <c r="J2" t="n">
         <v>1.7088</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>5.400700000000001</v>
+        <v>7.0887</v>
       </c>
       <c r="N2" t="n">
         <v>188</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1114</v>
+        <v>5.5167</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7607</v>
+        <v>1.9003</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6435</v>
+        <v>1.7539</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1114</v>
+        <v>5.5167</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5215</v>
+        <v>2.9268</v>
       </c>
       <c r="G3" t="n">
         <v>2.5899</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5215</v>
+        <v>2.9268</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5333</v>
+        <v>2.9514</v>
       </c>
       <c r="J3" t="n">
         <v>2.5899</v>
@@ -575,7 +575,7 @@
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>5.123200000000001</v>
+        <v>5.5413</v>
       </c>
       <c r="N3" t="n">
         <v>188</v>
@@ -584,139 +584,139 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2034</v>
+        <v>2.5099</v>
       </c>
       <c r="C4" t="n">
-        <v>0.759</v>
+        <v>0.8646</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4688</v>
+        <v>0.556</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2034</v>
+        <v>2.5099</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7374000000000001</v>
+        <v>2.5099</v>
       </c>
       <c r="G4" t="n">
-        <v>1.466</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7374000000000001</v>
+        <v>2.5099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7408</v>
+        <v>2.5099</v>
       </c>
       <c r="J4" t="n">
-        <v>1.466</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L4" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2068</v>
+        <v>2.5099</v>
       </c>
       <c r="N4" t="n">
-        <v>188</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5871</v>
+        <v>2.433</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5467</v>
+        <v>0.8381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2198</v>
+        <v>0.5254</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5871</v>
+        <v>2.433</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5871</v>
+        <v>2.433</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5871</v>
+        <v>2.433</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5871</v>
+        <v>2.433</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5871</v>
+        <v>2.433</v>
       </c>
       <c r="N5" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5571</v>
+        <v>2.2006</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5364</v>
+        <v>0.758</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2077</v>
+        <v>0.4328</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5571</v>
+        <v>2.2006</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5571</v>
+        <v>0.7346</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.466</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5571</v>
+        <v>0.7346</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5571</v>
+        <v>0.7408</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.466</v>
       </c>
       <c r="K6" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5571</v>
+        <v>2.2068</v>
       </c>
       <c r="N6" t="n">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.5337</v>
+        <v>1.8762</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5283</v>
+        <v>0.6463</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1982</v>
+        <v>0.3036</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5337</v>
+        <v>1.8762</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5337</v>
+        <v>1.8762</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5337</v>
+        <v>1.8762</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5337</v>
+        <v>1.8762</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5337</v>
+        <v>1.8762</v>
       </c>
       <c r="N7" t="n">
         <v>138</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.4642</v>
+        <v>1.7879</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5044</v>
+        <v>0.6159</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1701</v>
+        <v>0.2684</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4642</v>
+        <v>1.7879</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1437</v>
+        <v>1.7879</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3205</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1437</v>
+        <v>1.7879</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1437</v>
+        <v>1.7879</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3205</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4642</v>
+        <v>1.7879</v>
       </c>
       <c r="N8" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.134</v>
+        <v>1.4927</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3906</v>
+        <v>0.5142</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0367</v>
+        <v>0.1508</v>
       </c>
       <c r="E9" t="n">
-        <v>1.134</v>
+        <v>1.4927</v>
       </c>
       <c r="F9" t="n">
-        <v>1.134</v>
+        <v>1.1722</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.3205</v>
       </c>
       <c r="H9" t="n">
-        <v>1.134</v>
+        <v>1.1722</v>
       </c>
       <c r="I9" t="n">
-        <v>1.134</v>
+        <v>1.1722</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.3205</v>
       </c>
       <c r="K9" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.134</v>
+        <v>1.4927</v>
       </c>
       <c r="N9" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.0978</v>
+        <v>1.2391</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3782</v>
+        <v>0.4268</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0221</v>
+        <v>0.0497</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0978</v>
+        <v>1.2391</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2854</v>
+        <v>1.2391</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8124</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2854</v>
+        <v>1.2391</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2867</v>
+        <v>1.2391</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8124</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L10" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0991</v>
+        <v>1.2391</v>
       </c>
       <c r="N10" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.0259</v>
+        <v>1.0967</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3534</v>
+        <v>0.3778</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0069</v>
+        <v>-0.007</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0259</v>
+        <v>1.0967</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0259</v>
+        <v>0.2843</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.8124</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0259</v>
+        <v>0.2843</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0259</v>
+        <v>0.2867</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.8124</v>
       </c>
       <c r="K11" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0259</v>
+        <v>1.0991</v>
       </c>
       <c r="N11" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8427</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2903</v>
+        <v>0.3124</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0809</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8427</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8427</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8427</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8427</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8427</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>129</v>
@@ -998,369 +998,369 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6959</v>
+        <v>0.787</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2397</v>
+        <v>0.2711</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1402</v>
+        <v>-0.1304</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6959</v>
+        <v>0.787</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6959</v>
+        <v>1.787</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6959</v>
+        <v>1.787</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6959</v>
+        <v>1.787</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6959</v>
+        <v>0.7869999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5989</v>
+        <v>0.6959</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2063</v>
+        <v>0.2397</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1794</v>
+        <v>-0.1667</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5989</v>
+        <v>0.6959</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5989</v>
+        <v>0.6959</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5989</v>
+        <v>0.6959</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5989</v>
+        <v>0.6959</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5989</v>
+        <v>0.6959</v>
       </c>
       <c r="N14" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1964</v>
+        <v>0.2261</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1911</v>
+        <v>-0.1824</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6564</v>
       </c>
       <c r="N15" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="C16" t="n">
-        <v>0.187</v>
+        <v>0.2039</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2021</v>
+        <v>-0.2081</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="N16" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4747</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1635</v>
+        <v>0.187</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2296</v>
+        <v>-0.2277</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4747</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4747</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4747</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4747</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4747</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>142</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3268</v>
+        <v>0.4747</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1126</v>
+        <v>0.1635</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2893</v>
+        <v>-0.2548</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3268</v>
+        <v>0.4747</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7643</v>
+        <v>0.4747</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4375</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7643</v>
+        <v>0.4747</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7643</v>
+        <v>0.4747</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4375</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="L18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3268</v>
+        <v>0.4747</v>
       </c>
       <c r="N18" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2349</v>
+        <v>0.3271</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0809</v>
+        <v>0.1127</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3265</v>
+        <v>-0.3136</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2349</v>
+        <v>0.3271</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2349</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.4375</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2349</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2349</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.4375</v>
       </c>
       <c r="K19" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2349</v>
+        <v>0.3270999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2127</v>
+        <v>0.2349</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0733</v>
+        <v>0.0809</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3354</v>
+        <v>-0.3503</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2127</v>
+        <v>0.2349</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2127</v>
+        <v>0.2349</v>
       </c>
       <c r="G20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2127</v>
+        <v>0.2349</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2127</v>
+        <v>0.2349</v>
       </c>
       <c r="J20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2126999999999999</v>
+        <v>0.2349</v>
       </c>
       <c r="N20" t="n">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1863</v>
+        <v>0.1864</v>
       </c>
       <c r="C21" t="n">
         <v>0.06419999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3461</v>
+        <v>-0.3696</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1863</v>
+        <v>0.1864</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9087</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7224</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9087</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9087</v>
+        <v>0.9088000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>-0.7224</v>
@@ -1403,7 +1403,7 @@
         <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1862999999999999</v>
+        <v>0.1864</v>
       </c>
       <c r="N21" t="n">
         <v>185</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1114</v>
+        <v>0.1129</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0384</v>
+        <v>0.0389</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3764</v>
+        <v>-0.3989</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1114</v>
+        <v>0.1129</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1114</v>
+        <v>0.1129</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1114</v>
+        <v>0.1129</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1114</v>
+        <v>0.1129</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1114</v>
+        <v>0.1129</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1029</v>
+        <v>-0.1026</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0354</v>
+        <v>-0.0353</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4629</v>
+        <v>-0.4848</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1029</v>
+        <v>-0.1026</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1245</v>
+        <v>0.1248</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2274</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1245</v>
+        <v>0.1248</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1245</v>
+        <v>0.1248</v>
       </c>
       <c r="J23" t="n">
         <v>-0.2274</v>
@@ -1495,7 +1495,7 @@
         <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1029</v>
+        <v>-0.1026</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1504,185 +1504,185 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>valens</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1706</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0588</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5308</v>
+        <v>-0.5119</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1706</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1706</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1706</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1706</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1706</v>
       </c>
       <c r="N24" t="n">
-        <v>58</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>valens</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.3247</v>
+        <v>-0.2709</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1118</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5525</v>
+        <v>-0.5518</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3247</v>
+        <v>-0.2709</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3247</v>
+        <v>-0.2709</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3247</v>
+        <v>-0.2709</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3247</v>
+        <v>-0.2709</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.3247</v>
+        <v>-0.2709</v>
       </c>
       <c r="N25" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5856</v>
+        <v>-0.3136</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.2017</v>
+        <v>-0.108</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6579</v>
+        <v>-0.5688</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5856</v>
+        <v>-0.3136</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5856</v>
+        <v>-0.3136</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5856</v>
+        <v>-0.3136</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5856</v>
+        <v>-0.3136</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5856</v>
+        <v>-0.3136</v>
       </c>
       <c r="N26" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6237</v>
+        <v>-0.3247</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2148</v>
+        <v>-0.1118</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6733</v>
+        <v>-0.5733</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6237</v>
+        <v>-0.3247</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.6237</v>
+        <v>-0.3247</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6237</v>
+        <v>-0.3247</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6237</v>
+        <v>-0.3247</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6237</v>
+        <v>-0.3247</v>
       </c>
       <c r="N27" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28">
@@ -1698,7 +1698,7 @@
         <v>-0.2693</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7372</v>
+        <v>-0.7553</v>
       </c>
       <c r="E28" t="n">
         <v>-0.7817</v>
@@ -1744,7 +1744,7 @@
         <v>-0.3396</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8197</v>
+        <v>-0.8367</v>
       </c>
       <c r="E29" t="n">
         <v>-0.986</v>
@@ -1790,7 +1790,7 @@
         <v>-0.5675</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0869</v>
+        <v>-1.1002</v>
       </c>
       <c r="E30" t="n">
         <v>-1.6474</v>
@@ -1836,7 +1836,7 @@
         <v>-0.5977</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1223</v>
+        <v>-1.1352</v>
       </c>
       <c r="E31" t="n">
         <v>-1.7352</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.3253</v>
+        <v>-2.2547</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.801</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.3607</v>
+        <v>-1.3422</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.3253</v>
+        <v>-2.2547</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.4717</v>
+        <v>-1.4011</v>
       </c>
       <c r="G32" t="n">
         <v>-0.8536</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.4717</v>
+        <v>-1.4011</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.4785</v>
+        <v>-1.4129</v>
       </c>
       <c r="J32" t="n">
         <v>-0.8536</v>
@@ -1909,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="M32" t="n">
-        <v>-2.3321</v>
+        <v>-2.2665</v>
       </c>
       <c r="N32" t="n">
         <v>188</v>

--- a/database/event/3701/event_3701_evp_summary.xlsx
+++ b/database/event/3701/event_3701_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.58</v>
+        <v>5.4766</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2666</v>
+        <v>1.8865</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1776</v>
+        <v>1.8344</v>
       </c>
       <c r="E2" t="n">
-        <v>6.58</v>
+        <v>5.4766</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8712</v>
+        <v>3.782</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7088</v>
+        <v>1.6946</v>
       </c>
       <c r="H2" t="n">
-        <v>5.335</v>
+        <v>4.9449</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3799</v>
+        <v>5.1482</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7088</v>
+        <v>1.6946</v>
       </c>
       <c r="K2" t="n">
         <v>134</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>7.0887</v>
+        <v>6.8428</v>
       </c>
       <c r="N2" t="n">
         <v>188</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5167</v>
+        <v>5.287</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9003</v>
+        <v>1.8212</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7539</v>
+        <v>1.7488</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5167</v>
+        <v>5.287</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9268</v>
+        <v>2.899</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5899</v>
+        <v>2.388</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9268</v>
+        <v>3.0061</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9514</v>
+        <v>3.1297</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5899</v>
+        <v>2.388</v>
       </c>
       <c r="K3" t="n">
         <v>134</v>
@@ -575,7 +575,7 @@
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5413</v>
+        <v>5.5177</v>
       </c>
       <c r="N3" t="n">
         <v>188</v>
@@ -584,47 +584,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5099</v>
+        <v>2.6165</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8646</v>
+        <v>0.9013</v>
       </c>
       <c r="D4" t="n">
-        <v>0.556</v>
+        <v>0.5432</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5099</v>
+        <v>2.6165</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5099</v>
+        <v>1.067</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.5495</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5099</v>
+        <v>1.067</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5099</v>
+        <v>1.1109</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.5495</v>
       </c>
       <c r="K4" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5099</v>
+        <v>2.6604</v>
       </c>
       <c r="N4" t="n">
-        <v>138</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5">
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.433</v>
+        <v>2.597</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8381</v>
+        <v>0.8946</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5254</v>
+        <v>0.5344</v>
       </c>
       <c r="E5" t="n">
-        <v>2.433</v>
+        <v>2.597</v>
       </c>
       <c r="F5" t="n">
-        <v>2.433</v>
+        <v>2.597</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.433</v>
+        <v>2.597</v>
       </c>
       <c r="I5" t="n">
-        <v>2.433</v>
+        <v>2.597</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.433</v>
+        <v>2.597</v>
       </c>
       <c r="N5" t="n">
         <v>129</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.2006</v>
+        <v>2.421</v>
       </c>
       <c r="C6" t="n">
-        <v>0.758</v>
+        <v>0.834</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4328</v>
+        <v>0.4549</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2006</v>
+        <v>2.421</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7346</v>
+        <v>2.421</v>
       </c>
       <c r="G6" t="n">
-        <v>1.466</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7346</v>
+        <v>2.421</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7408</v>
+        <v>2.421</v>
       </c>
       <c r="J6" t="n">
-        <v>1.466</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.2068</v>
+        <v>2.421</v>
       </c>
       <c r="N6" t="n">
-        <v>188</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.8762</v>
+        <v>2.1606</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6463</v>
+        <v>0.7443</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3036</v>
+        <v>0.3374</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8762</v>
+        <v>2.1606</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8762</v>
+        <v>2.1606</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8762</v>
+        <v>2.1606</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8762</v>
+        <v>2.1606</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8762</v>
+        <v>2.1606</v>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.7879</v>
+        <v>2.0492</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6159</v>
+        <v>0.7059</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2684</v>
+        <v>0.2871</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7879</v>
+        <v>2.0492</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7879</v>
+        <v>2.0492</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7879</v>
+        <v>2.0492</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7879</v>
+        <v>2.0492</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7879</v>
+        <v>2.0492</v>
       </c>
       <c r="N8" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.4927</v>
+        <v>1.8575</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5142</v>
+        <v>0.6398</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1508</v>
+        <v>0.2006</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4927</v>
+        <v>1.8575</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1722</v>
+        <v>1.5005</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3205</v>
+        <v>0.357</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1722</v>
+        <v>1.5005</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1722</v>
+        <v>1.5005</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3205</v>
+        <v>0.357</v>
       </c>
       <c r="K9" t="n">
         <v>131</v>
@@ -851,7 +851,7 @@
         <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.4927</v>
+        <v>1.8575</v>
       </c>
       <c r="N9" t="n">
         <v>185</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.2391</v>
+        <v>1.7434</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4268</v>
+        <v>0.6005</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0497</v>
+        <v>0.149</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2391</v>
+        <v>1.7434</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2391</v>
+        <v>1.7434</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2391</v>
+        <v>1.7434</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2391</v>
+        <v>1.7434</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2391</v>
+        <v>1.7434</v>
       </c>
       <c r="N10" t="n">
         <v>142</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.0967</v>
+        <v>1.5445</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3778</v>
+        <v>0.532</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.007</v>
+        <v>0.0593</v>
       </c>
       <c r="E11" t="n">
-        <v>1.0967</v>
+        <v>1.5445</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2843</v>
+        <v>0.6501</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8124</v>
+        <v>0.8944</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2843</v>
+        <v>0.6501</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2867</v>
+        <v>0.6768</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8124</v>
+        <v>0.8944</v>
       </c>
       <c r="K11" t="n">
         <v>134</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0991</v>
+        <v>1.5712</v>
       </c>
       <c r="N11" t="n">
         <v>188</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3124</v>
+        <v>0.4794</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.0097</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9068000000000001</v>
+        <v>1.3918</v>
       </c>
       <c r="N12" t="n">
         <v>129</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.787</v>
+        <v>1.2363</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2711</v>
+        <v>0.4259</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1304</v>
+        <v>-0.0799</v>
       </c>
       <c r="E13" t="n">
-        <v>0.787</v>
+        <v>1.2363</v>
       </c>
       <c r="F13" t="n">
-        <v>1.787</v>
+        <v>1.9708</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>-0.7345</v>
       </c>
       <c r="H13" t="n">
-        <v>1.787</v>
+        <v>1.9708</v>
       </c>
       <c r="I13" t="n">
-        <v>1.787</v>
+        <v>1.9708</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>-0.7345</v>
       </c>
       <c r="K13" t="n">
         <v>131</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7869999999999999</v>
+        <v>1.2363</v>
       </c>
       <c r="N13" t="n">
         <v>185</v>
@@ -1044,93 +1044,93 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6959</v>
+        <v>1.1277</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2397</v>
+        <v>0.3885</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1667</v>
+        <v>-0.1289</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6959</v>
+        <v>1.1277</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6959</v>
+        <v>1.1277</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6959</v>
+        <v>1.1277</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6959</v>
+        <v>1.1277</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6959</v>
+        <v>1.1277</v>
       </c>
       <c r="N14" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6564</v>
+        <v>0.9326</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2261</v>
+        <v>0.3213</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1824</v>
+        <v>-0.217</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6564</v>
+        <v>0.9326</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6564</v>
+        <v>0.9326</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6564</v>
+        <v>0.9326</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6564</v>
+        <v>0.9326</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6564</v>
+        <v>0.9326</v>
       </c>
       <c r="N15" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5919</v>
+        <v>0.8941</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2039</v>
+        <v>0.308</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2081</v>
+        <v>-0.2344</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5919</v>
+        <v>0.8941</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5919</v>
+        <v>0.8941</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5919</v>
+        <v>0.8941</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5919</v>
+        <v>0.8941</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5919</v>
+        <v>0.8941</v>
       </c>
       <c r="N16" t="n">
         <v>129</v>
@@ -1182,127 +1182,127 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="C17" t="n">
-        <v>0.187</v>
+        <v>0.2987</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2277</v>
+        <v>-0.2466</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="N17" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4747</v>
+        <v>0.7912</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1635</v>
+        <v>0.2725</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2548</v>
+        <v>-0.2808</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4747</v>
+        <v>0.7912</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4747</v>
+        <v>0.7912</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4747</v>
+        <v>0.7912</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4747</v>
+        <v>0.7912</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4747</v>
+        <v>0.7912</v>
       </c>
       <c r="N18" t="n">
-        <v>142</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3271</v>
+        <v>0.734</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1127</v>
+        <v>0.2528</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3136</v>
+        <v>-0.3066</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3271</v>
+        <v>0.734</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7645999999999999</v>
+        <v>1.2074</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4375</v>
+        <v>-0.4734</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7645999999999999</v>
+        <v>1.2074</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7645999999999999</v>
+        <v>1.2074</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4375</v>
+        <v>-0.4734</v>
       </c>
       <c r="K19" t="n">
         <v>131</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3270999999999999</v>
+        <v>0.734</v>
       </c>
       <c r="N19" t="n">
         <v>185</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2349</v>
+        <v>0.7056</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0809</v>
+        <v>0.2431</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3503</v>
+        <v>-0.3195</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2349</v>
+        <v>0.7056</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2349</v>
+        <v>1.0227</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.3171</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2349</v>
+        <v>1.0227</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2349</v>
+        <v>1.0227</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.3171</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2349</v>
+        <v>0.7056</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1864</v>
+        <v>0.6694</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.2306</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3696</v>
+        <v>-0.3358</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1864</v>
+        <v>0.6694</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6694</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7224</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6694</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.6694</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7224</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1864</v>
+        <v>0.6694</v>
       </c>
       <c r="N21" t="n">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1129</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0389</v>
+        <v>0.2009</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3989</v>
+        <v>-0.3747</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1129</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1129</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1129</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1129</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1129</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1026</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0353</v>
+        <v>0.1741</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4848</v>
+        <v>-0.4098</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1026</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1248</v>
+        <v>0.5097</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2274</v>
+        <v>-0.0042</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1248</v>
+        <v>0.5097</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1248</v>
+        <v>0.5097</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2274</v>
+        <v>-0.0042</v>
       </c>
       <c r="K23" t="n">
         <v>131</v>
@@ -1495,7 +1495,7 @@
         <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1026</v>
+        <v>0.5055000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1706</v>
+        <v>0.3773</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0588</v>
+        <v>0.13</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5119</v>
+        <v>-0.4677</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1706</v>
+        <v>0.3773</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1706</v>
+        <v>0.3773</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1706</v>
+        <v>0.3773</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1706</v>
+        <v>0.3773</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1706</v>
+        <v>0.3773</v>
       </c>
       <c r="N24" t="n">
         <v>129</v>
@@ -1550,47 +1550,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>valens</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.2709</v>
+        <v>0.1735</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.0598</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5518</v>
+        <v>-0.5597</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.2709</v>
+        <v>0.1735</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2709</v>
+        <v>0.1735</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2709</v>
+        <v>0.1735</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2709</v>
+        <v>0.1735</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2709</v>
+        <v>0.1735</v>
       </c>
       <c r="N25" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3136</v>
+        <v>0.0357</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.108</v>
+        <v>0.0123</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5688</v>
+        <v>-0.6219</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3136</v>
+        <v>0.0357</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3136</v>
+        <v>0.0357</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3136</v>
+        <v>0.0357</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3136</v>
+        <v>0.0357</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3136</v>
+        <v>0.0357</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>valens</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3247</v>
+        <v>-0.0684</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1118</v>
+        <v>-0.0236</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5733</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3247</v>
+        <v>-0.0684</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3247</v>
+        <v>-0.0684</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3247</v>
+        <v>-0.0684</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3247</v>
+        <v>-0.0684</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3247</v>
+        <v>-0.0684</v>
       </c>
       <c r="N27" t="n">
-        <v>132</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7817</v>
+        <v>-0.2995</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2693</v>
+        <v>-0.1032</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7553</v>
+        <v>-0.7732</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7817</v>
+        <v>-0.2995</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7817</v>
+        <v>-0.2995</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7817</v>
+        <v>-0.2995</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7817</v>
+        <v>-0.2995</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7817</v>
+        <v>-0.2995</v>
       </c>
       <c r="N28" t="n">
         <v>132</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.986</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3396</v>
+        <v>-0.1919</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8367</v>
+        <v>-0.8895</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.986</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.986</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.986</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.986</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.986</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>132</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.6474</v>
+        <v>-1.0482</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.5675</v>
+        <v>-0.3611</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1002</v>
+        <v>-1.1112</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.6474</v>
+        <v>-1.0482</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.6474</v>
+        <v>-1.0482</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.6474</v>
+        <v>-1.0482</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.6474</v>
+        <v>-1.0482</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.6474</v>
+        <v>-1.0482</v>
       </c>
       <c r="N30" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.7352</v>
+        <v>-1.0528</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.5977</v>
+        <v>-0.3627</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1352</v>
+        <v>-1.1133</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.7352</v>
+        <v>-1.0528</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.7352</v>
+        <v>-1.0528</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.7352</v>
+        <v>-1.0528</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.7352</v>
+        <v>-1.0528</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.7352</v>
+        <v>-1.0528</v>
       </c>
       <c r="N31" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-2.2547</v>
+        <v>-1.7638</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.6076</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.3422</v>
+        <v>-1.4343</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.2547</v>
+        <v>-1.7638</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.4011</v>
+        <v>-1.0233</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.8536</v>
+        <v>-0.7405</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.4011</v>
+        <v>-1.0233</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.4129</v>
+        <v>-1.0654</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8536</v>
+        <v>-0.7405</v>
       </c>
       <c r="K32" t="n">
         <v>134</v>
@@ -1909,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="M32" t="n">
-        <v>-2.2665</v>
+        <v>-1.8059</v>
       </c>
       <c r="N32" t="n">
         <v>188</v>
@@ -2015,10 +2015,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0596</v>
+        <v>-0.0785</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.5496</v>
+        <v>-2.041</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2055,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2237</v>
+        <v>-0.193</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.8162</v>
+        <v>-5.018</v>
       </c>
     </row>
     <row r="4">
@@ -2095,10 +2095,10 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5634</v>
+        <v>-0.3842</v>
       </c>
       <c r="J4" t="n">
-        <v>-14.6484</v>
+        <v>-9.9892</v>
       </c>
     </row>
     <row r="5">
@@ -2135,10 +2135,10 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5634</v>
+        <v>-0.3842</v>
       </c>
       <c r="J5" t="n">
-        <v>-14.6484</v>
+        <v>-9.9892</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2175,10 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7685999999999999</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-19.9836</v>
+        <v>-13.6422</v>
       </c>
     </row>
     <row r="7">
@@ -2215,10 +2215,10 @@
         <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3282</v>
+        <v>1.2254</v>
       </c>
       <c r="J7" t="n">
-        <v>34.5332</v>
+        <v>31.8604</v>
       </c>
     </row>
     <row r="8">
@@ -2255,10 +2255,10 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0649</v>
+        <v>1.0686</v>
       </c>
       <c r="J8" t="n">
-        <v>27.6874</v>
+        <v>27.7836</v>
       </c>
     </row>
     <row r="9">
@@ -2295,10 +2295,10 @@
         <v>1.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0432</v>
+        <v>1.0562</v>
       </c>
       <c r="J9" t="n">
-        <v>27.1232</v>
+        <v>27.4612</v>
       </c>
     </row>
     <row r="10">
@@ -2335,10 +2335,10 @@
         <v>1.32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6999</v>
+        <v>0.8022</v>
       </c>
       <c r="J10" t="n">
-        <v>18.1974</v>
+        <v>20.8572</v>
       </c>
     </row>
     <row r="11">
@@ -2375,10 +2375,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1926</v>
+        <v>0.2865</v>
       </c>
       <c r="J11" t="n">
-        <v>5.0076</v>
+        <v>7.449</v>
       </c>
     </row>
     <row r="12">
@@ -2415,10 +2415,10 @@
         <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3801</v>
+        <v>0.4355</v>
       </c>
       <c r="J12" t="n">
-        <v>10.6428</v>
+        <v>12.194</v>
       </c>
     </row>
     <row r="13">
@@ -2455,10 +2455,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.336</v>
+        <v>0.38</v>
       </c>
       <c r="J13" t="n">
-        <v>9.407999999999999</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="14">
@@ -2495,10 +2495,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.159</v>
+        <v>-0.0892</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.452</v>
+        <v>-2.4976</v>
       </c>
     </row>
     <row r="15">
@@ -2535,10 +2535,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2138</v>
+        <v>-0.1241</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.9864</v>
+        <v>-3.4748</v>
       </c>
     </row>
     <row r="16">
@@ -2575,10 +2575,10 @@
         <v>0.83</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.342</v>
+        <v>-0.2098</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.576000000000001</v>
+        <v>-5.8744</v>
       </c>
     </row>
     <row r="17">
@@ -2615,10 +2615,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2617</v>
+        <v>1.1626</v>
       </c>
       <c r="J17" t="n">
-        <v>35.3276</v>
+        <v>32.5528</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2655,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7661</v>
+        <v>0.7473</v>
       </c>
       <c r="J18" t="n">
-        <v>21.4508</v>
+        <v>20.9244</v>
       </c>
     </row>
     <row r="19">
@@ -2695,10 +2695,10 @@
         <v>1.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6439</v>
+        <v>0.626</v>
       </c>
       <c r="J19" t="n">
-        <v>18.0292</v>
+        <v>17.528</v>
       </c>
     </row>
     <row r="20">
@@ -2735,10 +2735,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2308</v>
+        <v>-0.1618</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.4624</v>
+        <v>-4.5304</v>
       </c>
     </row>
     <row r="21">
@@ -2775,10 +2775,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0462</v>
+        <v>-1.027</v>
       </c>
       <c r="J21" t="n">
-        <v>-29.2936</v>
+        <v>-28.756</v>
       </c>
     </row>
     <row r="22">
@@ -2815,10 +2815,10 @@
         <v>1.24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4345</v>
+        <v>0.5059</v>
       </c>
       <c r="J22" t="n">
-        <v>13.035</v>
+        <v>15.177</v>
       </c>
     </row>
     <row r="23">
@@ -2855,10 +2855,10 @@
         <v>1.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3924</v>
+        <v>0.4519</v>
       </c>
       <c r="J23" t="n">
-        <v>11.772</v>
+        <v>13.557</v>
       </c>
     </row>
     <row r="24">
@@ -2895,10 +2895,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2328</v>
+        <v>-0.136</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.984</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="25">
@@ -2935,10 +2935,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.282</v>
+        <v>-0.1687</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.460000000000001</v>
+        <v>-5.061</v>
       </c>
     </row>
     <row r="26">
@@ -2975,10 +2975,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2977</v>
+        <v>-0.1793</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.930999999999999</v>
+        <v>-5.379</v>
       </c>
     </row>
     <row r="27">
@@ -3015,10 +3015,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9304</v>
+        <v>0.9091</v>
       </c>
       <c r="J27" t="n">
-        <v>27.912</v>
+        <v>27.273</v>
       </c>
     </row>
     <row r="28">
@@ -3055,10 +3055,10 @@
         <v>1.08</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2733</v>
+        <v>0.2713</v>
       </c>
       <c r="J28" t="n">
-        <v>8.199</v>
+        <v>8.138999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3095,10 +3095,10 @@
         <v>1.06</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1913</v>
+        <v>0.2133</v>
       </c>
       <c r="J29" t="n">
-        <v>5.739</v>
+        <v>6.399</v>
       </c>
     </row>
     <row r="30">
@@ -3135,10 +3135,10 @@
         <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0048</v>
+        <v>0.0383</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.144</v>
+        <v>1.149</v>
       </c>
     </row>
     <row r="31">
@@ -3175,10 +3175,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4603</v>
+        <v>-0.3988</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.809</v>
+        <v>-11.964</v>
       </c>
     </row>
     <row r="32">
@@ -3215,10 +3215,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9113</v>
+        <v>0.9196</v>
       </c>
       <c r="J32" t="n">
-        <v>23.6938</v>
+        <v>23.9096</v>
       </c>
     </row>
     <row r="33">
@@ -3255,10 +3255,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8662</v>
+        <v>0.8756</v>
       </c>
       <c r="J33" t="n">
-        <v>22.5212</v>
+        <v>22.7656</v>
       </c>
     </row>
     <row r="34">
@@ -3295,10 +3295,10 @@
         <v>1.3</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7853</v>
       </c>
       <c r="J34" t="n">
-        <v>20.0902</v>
+        <v>20.4178</v>
       </c>
     </row>
     <row r="35">
@@ -3335,10 +3335,10 @@
         <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2214</v>
+        <v>0.295</v>
       </c>
       <c r="J35" t="n">
-        <v>5.7564</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="36">
@@ -3375,10 +3375,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1025</v>
+        <v>0.1763</v>
       </c>
       <c r="J36" t="n">
-        <v>2.665</v>
+        <v>4.5838</v>
       </c>
     </row>
     <row r="37">
@@ -3415,10 +3415,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4204</v>
+        <v>0.4765</v>
       </c>
       <c r="J37" t="n">
-        <v>10.9304</v>
+        <v>12.389</v>
       </c>
     </row>
     <row r="38">
@@ -3455,10 +3455,10 @@
         <v>0.84</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2728</v>
+        <v>-0.1822</v>
       </c>
       <c r="J38" t="n">
-        <v>-7.0928</v>
+        <v>-4.7372</v>
       </c>
     </row>
     <row r="39">
@@ -3495,10 +3495,10 @@
         <v>0.83</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2906</v>
+        <v>-0.1921</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.5556</v>
+        <v>-4.9946</v>
       </c>
     </row>
     <row r="40">
@@ -3535,10 +3535,10 @@
         <v>0.73</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4464</v>
+        <v>-0.2901</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.6064</v>
+        <v>-7.5426</v>
       </c>
     </row>
     <row r="41">
@@ -3575,10 +3575,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4748</v>
+        <v>-0.3093</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.3448</v>
+        <v>-8.0418</v>
       </c>
     </row>
     <row r="42">
@@ -3615,10 +3615,10 @@
         <v>1.53</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2404</v>
+        <v>1.1601</v>
       </c>
       <c r="J42" t="n">
-        <v>28.5292</v>
+        <v>26.6823</v>
       </c>
     </row>
     <row r="43">
@@ -3655,10 +3655,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9485</v>
+        <v>0.9665</v>
       </c>
       <c r="J43" t="n">
-        <v>21.8155</v>
+        <v>22.2295</v>
       </c>
     </row>
     <row r="44">
@@ -3695,10 +3695,10 @@
         <v>1.29</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7058</v>
+        <v>0.7528</v>
       </c>
       <c r="J44" t="n">
-        <v>16.2334</v>
+        <v>17.3144</v>
       </c>
     </row>
     <row r="45">
@@ -3735,10 +3735,10 @@
         <v>1.18</v>
       </c>
       <c r="I45" t="n">
-        <v>0.412</v>
+        <v>0.4949</v>
       </c>
       <c r="J45" t="n">
-        <v>9.476000000000001</v>
+        <v>11.3827</v>
       </c>
     </row>
     <row r="46">
@@ -3775,10 +3775,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0189</v>
+        <v>0.0984</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4347</v>
+        <v>2.2632</v>
       </c>
     </row>
     <row r="47">
@@ -3815,10 +3815,10 @@
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1815</v>
+        <v>0.1645</v>
       </c>
       <c r="J47" t="n">
-        <v>4.1745</v>
+        <v>3.7835</v>
       </c>
     </row>
     <row r="48">
@@ -3855,10 +3855,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0789</v>
+        <v>0.0413</v>
       </c>
       <c r="J48" t="n">
-        <v>1.8147</v>
+        <v>0.9499</v>
       </c>
     </row>
     <row r="49">
@@ -3895,10 +3895,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2522</v>
+        <v>-0.1805</v>
       </c>
       <c r="J49" t="n">
-        <v>-5.8006</v>
+        <v>-4.1515</v>
       </c>
     </row>
     <row r="50">
@@ -3935,10 +3935,10 @@
         <v>0.75</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4096</v>
+        <v>-0.2679</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.4208</v>
+        <v>-6.1617</v>
       </c>
     </row>
     <row r="51">
@@ -3975,10 +3975,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6676</v>
+        <v>-0.4471</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.3548</v>
+        <v>-10.2833</v>
       </c>
     </row>
     <row r="52">
@@ -4015,10 +4015,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0554</v>
+        <v>1.0307</v>
       </c>
       <c r="J52" t="n">
-        <v>31.662</v>
+        <v>30.921</v>
       </c>
     </row>
     <row r="53">
@@ -4055,10 +4055,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7892</v>
+        <v>0.7809</v>
       </c>
       <c r="J53" t="n">
-        <v>23.676</v>
+        <v>23.427</v>
       </c>
     </row>
     <row r="54">
@@ -4095,10 +4095,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5068</v>
+        <v>0.5174</v>
       </c>
       <c r="J54" t="n">
-        <v>15.204</v>
+        <v>15.522</v>
       </c>
     </row>
     <row r="55">
@@ -4135,10 +4135,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.008</v>
+        <v>0.0564</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.24</v>
+        <v>1.692</v>
       </c>
     </row>
     <row r="56">
@@ -4175,10 +4175,10 @@
         <v>0.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.408</v>
+        <v>-0.3352</v>
       </c>
       <c r="J56" t="n">
-        <v>-12.24</v>
+        <v>-10.056</v>
       </c>
     </row>
     <row r="57">
@@ -4215,10 +4215,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.6737</v>
       </c>
       <c r="J57" t="n">
-        <v>16.83</v>
+        <v>20.211</v>
       </c>
     </row>
     <row r="58">
@@ -4255,10 +4255,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2655</v>
+        <v>0.2981</v>
       </c>
       <c r="J58" t="n">
-        <v>7.965</v>
+        <v>8.943</v>
       </c>
     </row>
     <row r="59">
@@ -4295,10 +4295,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1975</v>
+        <v>0.2188</v>
       </c>
       <c r="J59" t="n">
-        <v>5.925</v>
+        <v>6.564</v>
       </c>
     </row>
     <row r="60">
@@ -4335,10 +4335,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2374</v>
+        <v>-0.1378</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.122</v>
+        <v>-4.134</v>
       </c>
     </row>
     <row r="61">
@@ -4375,10 +4375,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5258</v>
+        <v>-0.3398</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.774</v>
+        <v>-10.194</v>
       </c>
     </row>
     <row r="62">
@@ -4415,10 +4415,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4212</v>
+        <v>0.48</v>
       </c>
       <c r="J62" t="n">
-        <v>9.6876</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="63">
@@ -4455,10 +4455,10 @@
         <v>0.76</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.338</v>
+        <v>-0.2485</v>
       </c>
       <c r="J63" t="n">
-        <v>-7.774</v>
+        <v>-5.7155</v>
       </c>
     </row>
     <row r="64">
@@ -4495,10 +4495,10 @@
         <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4953</v>
+        <v>-0.3319</v>
       </c>
       <c r="J64" t="n">
-        <v>-11.3919</v>
+        <v>-7.6337</v>
       </c>
     </row>
     <row r="65">
@@ -4535,10 +4535,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4953</v>
+        <v>-0.3319</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.3919</v>
+        <v>-7.6337</v>
       </c>
     </row>
     <row r="66">
@@ -4575,10 +4575,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7247</v>
+        <v>-0.4907</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.6681</v>
+        <v>-11.2861</v>
       </c>
     </row>
     <row r="67">
@@ -4615,10 +4615,10 @@
         <v>1.76</v>
       </c>
       <c r="I67" t="n">
-        <v>1.6157</v>
+        <v>1.4096</v>
       </c>
       <c r="J67" t="n">
-        <v>37.1611</v>
+        <v>32.4208</v>
       </c>
     </row>
     <row r="68">
@@ -4655,10 +4655,10 @@
         <v>1.5</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1168</v>
+        <v>1.1023</v>
       </c>
       <c r="J68" t="n">
-        <v>25.6864</v>
+        <v>25.3529</v>
       </c>
     </row>
     <row r="69">
@@ -4695,10 +4695,10 @@
         <v>1.42</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9347</v>
+        <v>0.9978</v>
       </c>
       <c r="J69" t="n">
-        <v>21.4981</v>
+        <v>22.9494</v>
       </c>
     </row>
     <row r="70">
@@ -4735,10 +4735,10 @@
         <v>1.22</v>
       </c>
       <c r="I70" t="n">
-        <v>0.4592</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>10.5616</v>
+        <v>13.018</v>
       </c>
     </row>
     <row r="71">
@@ -4775,10 +4775,10 @@
         <v>1.17</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3392</v>
+        <v>0.4416</v>
       </c>
       <c r="J71" t="n">
-        <v>7.8016</v>
+        <v>10.1568</v>
       </c>
     </row>
     <row r="72">
@@ -4815,10 +4815,10 @@
         <v>1.42</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6788</v>
+        <v>0.8335</v>
       </c>
       <c r="J72" t="n">
-        <v>16.97</v>
+        <v>20.8375</v>
       </c>
     </row>
     <row r="73">
@@ -4855,10 +4855,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5029</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J73" t="n">
-        <v>12.5725</v>
+        <v>14.805</v>
       </c>
     </row>
     <row r="74">
@@ -4895,10 +4895,10 @@
         <v>0.82</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3477</v>
+        <v>-0.2158</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.692500000000001</v>
+        <v>-5.395</v>
       </c>
     </row>
     <row r="75">
@@ -4935,10 +4935,10 @@
         <v>0.76</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4343</v>
+        <v>-0.2755</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.8575</v>
+        <v>-6.8875</v>
       </c>
     </row>
     <row r="76">
@@ -4975,10 +4975,10 @@
         <v>0.59</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6542</v>
+        <v>-0.4356</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.355</v>
+        <v>-10.89</v>
       </c>
     </row>
     <row r="77">
@@ -5015,10 +5015,10 @@
         <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>0.636</v>
+        <v>0.5996</v>
       </c>
       <c r="J77" t="n">
-        <v>15.9</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="78">
@@ -5055,10 +5055,10 @@
         <v>1.12</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4197</v>
+        <v>0.3884</v>
       </c>
       <c r="J78" t="n">
-        <v>10.4925</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5095,10 +5095,10 @@
         <v>1.03</v>
       </c>
       <c r="I79" t="n">
-        <v>0.0969</v>
+        <v>0.1205</v>
       </c>
       <c r="J79" t="n">
-        <v>2.4225</v>
+        <v>3.0125</v>
       </c>
     </row>
     <row r="80">
@@ -5135,10 +5135,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1124</v>
+        <v>-0.0653</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.81</v>
+        <v>-1.6325</v>
       </c>
     </row>
     <row r="81">
@@ -5175,10 +5175,10 @@
         <v>0.92</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3631</v>
+        <v>-0.3048</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.077500000000001</v>
+        <v>-7.62</v>
       </c>
     </row>
     <row r="82">
@@ -5215,10 +5215,10 @@
         <v>1.9</v>
       </c>
       <c r="I82" t="n">
-        <v>1.9125</v>
+        <v>1.6119</v>
       </c>
       <c r="J82" t="n">
-        <v>47.8125</v>
+        <v>40.2975</v>
       </c>
     </row>
     <row r="83">
@@ -5255,10 +5255,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.5764</v>
+        <v>0.6435</v>
       </c>
       <c r="J83" t="n">
-        <v>14.41</v>
+        <v>16.0875</v>
       </c>
     </row>
     <row r="84">
@@ -5295,10 +5295,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.4465</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>11.1625</v>
+        <v>13.0925</v>
       </c>
     </row>
     <row r="85">
@@ -5335,10 +5335,10 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3947</v>
+        <v>0.4736</v>
       </c>
       <c r="J85" t="n">
-        <v>9.8675</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="86">
@@ -5375,10 +5375,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6496</v>
+        <v>-0.5859</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.24</v>
+        <v>-14.6475</v>
       </c>
     </row>
     <row r="87">
@@ -5415,10 +5415,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3602</v>
+        <v>0.3948</v>
       </c>
       <c r="J87" t="n">
-        <v>9.005000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5455,10 +5455,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2703</v>
+        <v>-0.2047</v>
       </c>
       <c r="J88" t="n">
-        <v>-6.7575</v>
+        <v>-5.1175</v>
       </c>
     </row>
     <row r="89">
@@ -5495,10 +5495,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3085</v>
+        <v>-0.2238</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.7125</v>
+        <v>-5.595</v>
       </c>
     </row>
     <row r="90">
@@ -5535,10 +5535,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5636</v>
+        <v>-0.3746</v>
       </c>
       <c r="J90" t="n">
-        <v>-14.09</v>
+        <v>-9.365</v>
       </c>
     </row>
     <row r="91">
@@ -5575,10 +5575,10 @@
         <v>0.57</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6433</v>
+        <v>-0.4307</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.0825</v>
+        <v>-10.7675</v>
       </c>
     </row>
     <row r="92">
@@ -5615,10 +5615,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.975</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="J92" t="n">
-        <v>28.275</v>
+        <v>27.9618</v>
       </c>
     </row>
     <row r="93">
@@ -5655,10 +5655,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6743</v>
+        <v>0.6653</v>
       </c>
       <c r="J93" t="n">
-        <v>19.5547</v>
+        <v>19.2937</v>
       </c>
     </row>
     <row r="94">
@@ -5695,10 +5695,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3219</v>
+        <v>0.3677</v>
       </c>
       <c r="J94" t="n">
-        <v>9.335100000000001</v>
+        <v>10.6633</v>
       </c>
     </row>
     <row r="95">
@@ -5735,10 +5735,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3219</v>
+        <v>0.3677</v>
       </c>
       <c r="J95" t="n">
-        <v>9.335100000000001</v>
+        <v>10.6633</v>
       </c>
     </row>
     <row r="96">
@@ -5775,10 +5775,10 @@
         <v>0.92</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4046</v>
+        <v>-0.3326</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.7334</v>
+        <v>-9.6454</v>
       </c>
     </row>
     <row r="97">
@@ -5815,10 +5815,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7704</v>
+        <v>0.9671</v>
       </c>
       <c r="J97" t="n">
-        <v>22.3416</v>
+        <v>28.0459</v>
       </c>
     </row>
     <row r="98">
@@ -5855,10 +5855,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0713</v>
+        <v>0.0347</v>
       </c>
       <c r="J98" t="n">
-        <v>2.0677</v>
+        <v>1.0063</v>
       </c>
     </row>
     <row r="99">
@@ -5895,10 +5895,10 @@
         <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.386</v>
+        <v>-0.2508</v>
       </c>
       <c r="J99" t="n">
-        <v>-11.194</v>
+        <v>-7.2732</v>
       </c>
     </row>
     <row r="100">
@@ -5935,10 +5935,10 @@
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6586</v>
+        <v>-0.4402</v>
       </c>
       <c r="J100" t="n">
-        <v>-19.0994</v>
+        <v>-12.7658</v>
       </c>
     </row>
     <row r="101">
@@ -5975,10 +5975,10 @@
         <v>0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7683</v>
+        <v>-0.5226</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.2807</v>
+        <v>-15.1554</v>
       </c>
     </row>
     <row r="102">
@@ -6015,10 +6015,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2214</v>
+        <v>1.1524</v>
       </c>
       <c r="J102" t="n">
-        <v>24.428</v>
+        <v>23.048</v>
       </c>
     </row>
     <row r="103">
@@ -6055,10 +6055,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7164</v>
+        <v>0.7915</v>
       </c>
       <c r="J103" t="n">
-        <v>14.328</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="104">
@@ -6095,10 +6095,10 @@
         <v>1.28</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6405</v>
+        <v>0.7248</v>
       </c>
       <c r="J104" t="n">
-        <v>12.81</v>
+        <v>14.496</v>
       </c>
     </row>
     <row r="105">
@@ -6135,10 +6135,10 @@
         <v>1.28</v>
       </c>
       <c r="I105" t="n">
-        <v>0.6405</v>
+        <v>0.7248</v>
       </c>
       <c r="J105" t="n">
-        <v>12.81</v>
+        <v>14.496</v>
       </c>
     </row>
     <row r="106">
@@ -6175,10 +6175,10 @@
         <v>1.23</v>
       </c>
       <c r="I106" t="n">
-        <v>0.5182</v>
+        <v>0.6087</v>
       </c>
       <c r="J106" t="n">
-        <v>10.364</v>
+        <v>12.174</v>
       </c>
     </row>
     <row r="107">
@@ -6215,10 +6215,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.423</v>
+        <v>0.4828</v>
       </c>
       <c r="J107" t="n">
-        <v>8.460000000000001</v>
+        <v>9.656000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6255,10 +6255,10 @@
         <v>0.85</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.182</v>
+        <v>-0.157</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.64</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="109">
@@ -6295,10 +6295,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3794</v>
+        <v>-0.2661</v>
       </c>
       <c r="J109" t="n">
-        <v>-7.588</v>
+        <v>-5.322</v>
       </c>
     </row>
     <row r="110">
@@ -6335,10 +6335,10 @@
         <v>0.5</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7238</v>
+        <v>-0.4902</v>
       </c>
       <c r="J110" t="n">
-        <v>-14.476</v>
+        <v>-9.804</v>
       </c>
     </row>
     <row r="111">
@@ -6375,10 +6375,10 @@
         <v>0.49</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.4994</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.728</v>
+        <v>-9.988</v>
       </c>
     </row>
     <row r="112">
@@ -6415,10 +6415,10 @@
         <v>1.37</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9718</v>
+        <v>0.9623</v>
       </c>
       <c r="J112" t="n">
-        <v>28.1822</v>
+        <v>27.9067</v>
       </c>
     </row>
     <row r="113">
@@ -6455,10 +6455,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4447</v>
+        <v>0.4692</v>
       </c>
       <c r="J113" t="n">
-        <v>12.8963</v>
+        <v>13.6068</v>
       </c>
     </row>
     <row r="114">
@@ -6495,10 +6495,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2879</v>
+        <v>0.3394</v>
       </c>
       <c r="J114" t="n">
-        <v>8.3491</v>
+        <v>9.842599999999999</v>
       </c>
     </row>
     <row r="115">
@@ -6535,10 +6535,10 @@
         <v>1.11</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2879</v>
+        <v>0.3394</v>
       </c>
       <c r="J115" t="n">
-        <v>8.3491</v>
+        <v>9.842599999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6575,10 +6575,10 @@
         <v>1.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1015</v>
+        <v>0.1622</v>
       </c>
       <c r="J116" t="n">
-        <v>2.9435</v>
+        <v>4.7038</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5027</v>
+        <v>0.5891</v>
       </c>
       <c r="J117" t="n">
-        <v>14.5783</v>
+        <v>17.0839</v>
       </c>
     </row>
     <row r="118">
@@ -6655,10 +6655,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0669</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.1286</v>
+        <v>-1.9401</v>
       </c>
     </row>
     <row r="119">
@@ -6695,10 +6695,10 @@
         <v>0.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1141</v>
+        <v>-0.0911</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.3089</v>
+        <v>-2.6419</v>
       </c>
     </row>
     <row r="120">
@@ -6735,10 +6735,10 @@
         <v>0.77</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4007</v>
+        <v>-0.2565</v>
       </c>
       <c r="J120" t="n">
-        <v>-11.6203</v>
+        <v>-7.4385</v>
       </c>
     </row>
     <row r="121">
@@ -6775,10 +6775,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.642</v>
+        <v>-0.4272</v>
       </c>
       <c r="J121" t="n">
-        <v>-18.618</v>
+        <v>-12.3888</v>
       </c>
     </row>
     <row r="122">
@@ -6815,10 +6815,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.397</v>
+        <v>0.4616</v>
       </c>
       <c r="J122" t="n">
-        <v>11.91</v>
+        <v>13.848</v>
       </c>
     </row>
     <row r="123">
@@ -6855,10 +6855,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3238</v>
+        <v>0.3707</v>
       </c>
       <c r="J123" t="n">
-        <v>9.714</v>
+        <v>11.121</v>
       </c>
     </row>
     <row r="124">
@@ -6895,10 +6895,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.134</v>
+        <v>0.1539</v>
       </c>
       <c r="J124" t="n">
-        <v>4.02</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="125">
@@ -6935,10 +6935,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0844</v>
+        <v>0.1099</v>
       </c>
       <c r="J125" t="n">
-        <v>2.532</v>
+        <v>3.297</v>
       </c>
     </row>
     <row r="126">
@@ -6975,10 +6975,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4887</v>
+        <v>-0.3125</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.661</v>
+        <v>-9.375</v>
       </c>
     </row>
     <row r="127">
@@ -7015,10 +7015,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9393</v>
+        <v>0.9164</v>
       </c>
       <c r="J127" t="n">
-        <v>28.179</v>
+        <v>27.492</v>
       </c>
     </row>
     <row r="128">
@@ -7055,10 +7055,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2551</v>
+        <v>0.2451</v>
       </c>
       <c r="J128" t="n">
-        <v>7.653</v>
+        <v>7.353</v>
       </c>
     </row>
     <row r="129">
@@ -7095,10 +7095,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1192</v>
       </c>
       <c r="J129" t="n">
-        <v>2.754</v>
+        <v>3.576</v>
       </c>
     </row>
     <row r="130">
@@ -7135,10 +7135,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1192</v>
       </c>
       <c r="J130" t="n">
-        <v>2.754</v>
+        <v>3.576</v>
       </c>
     </row>
     <row r="131">
@@ -7175,10 +7175,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.614</v>
+        <v>-0.5592</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.42</v>
+        <v>-16.776</v>
       </c>
     </row>
     <row r="132">
@@ -7215,10 +7215,10 @@
         <v>1.65</v>
       </c>
       <c r="I132" t="n">
-        <v>1.5433</v>
+        <v>1.3512</v>
       </c>
       <c r="J132" t="n">
-        <v>37.0392</v>
+        <v>32.4288</v>
       </c>
     </row>
     <row r="133">
@@ -7255,10 +7255,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4423</v>
+        <v>0.4477</v>
       </c>
       <c r="J133" t="n">
-        <v>10.6152</v>
+        <v>10.7448</v>
       </c>
     </row>
     <row r="134">
@@ -7295,10 +7295,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.0322</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.3328</v>
+        <v>-0.7728</v>
       </c>
     </row>
     <row r="135">
@@ -7335,10 +7335,10 @@
         <v>0.96</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2721</v>
+        <v>-0.2005</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.5304</v>
+        <v>-4.812</v>
       </c>
     </row>
     <row r="136">
@@ -7375,10 +7375,10 @@
         <v>0.92</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3982</v>
+        <v>-0.3279</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.556800000000001</v>
+        <v>-7.8696</v>
       </c>
     </row>
     <row r="137">
@@ -7415,10 +7415,10 @@
         <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5375</v>
+        <v>0.6378</v>
       </c>
       <c r="J137" t="n">
-        <v>12.9</v>
+        <v>15.3072</v>
       </c>
     </row>
     <row r="138">
@@ -7455,10 +7455,10 @@
         <v>1.24</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4573</v>
+        <v>0.5301</v>
       </c>
       <c r="J138" t="n">
-        <v>10.9752</v>
+        <v>12.7224</v>
       </c>
     </row>
     <row r="139">
@@ -7495,10 +7495,10 @@
         <v>0.78</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4001</v>
+        <v>-0.2529</v>
       </c>
       <c r="J139" t="n">
-        <v>-9.602399999999999</v>
+        <v>-6.0696</v>
       </c>
     </row>
     <row r="140">
@@ -7535,10 +7535,10 @@
         <v>0.72</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4837</v>
+        <v>-0.3113</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.6088</v>
+        <v>-7.4712</v>
       </c>
     </row>
     <row r="141">
@@ -7575,10 +7575,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4972</v>
+        <v>-0.3209</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.9328</v>
+        <v>-7.7016</v>
       </c>
     </row>
     <row r="142">
@@ -7615,10 +7615,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7604</v>
+        <v>0.9458</v>
       </c>
       <c r="J142" t="n">
-        <v>22.812</v>
+        <v>28.374</v>
       </c>
     </row>
     <row r="143">
@@ -7655,10 +7655,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.241</v>
+        <v>0.2641</v>
       </c>
       <c r="J143" t="n">
-        <v>7.23</v>
+        <v>7.923</v>
       </c>
     </row>
     <row r="144">
@@ -7695,10 +7695,10 @@
         <v>0.98</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0731</v>
+        <v>-0.0368</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.193</v>
+        <v>-1.104</v>
       </c>
     </row>
     <row r="145">
@@ -7735,10 +7735,10 @@
         <v>0.73</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4826</v>
+        <v>-0.3087</v>
       </c>
       <c r="J145" t="n">
-        <v>-14.478</v>
+        <v>-9.260999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -7775,10 +7775,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4826</v>
+        <v>-0.3087</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.478</v>
+        <v>-9.260999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -7815,10 +7815,10 @@
         <v>1.59</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4597</v>
+        <v>1.2943</v>
       </c>
       <c r="J147" t="n">
-        <v>43.791</v>
+        <v>38.829</v>
       </c>
     </row>
     <row r="148">
@@ -7855,10 +7855,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1856</v>
+        <v>0.2122</v>
       </c>
       <c r="J148" t="n">
-        <v>5.568</v>
+        <v>6.366</v>
       </c>
     </row>
     <row r="149">
@@ -7895,10 +7895,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.129</v>
+        <v>-0.0725</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.87</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="150">
@@ -7935,10 +7935,10 @@
         <v>0.97</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2111</v>
+        <v>-0.1506</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.333</v>
+        <v>-4.518</v>
       </c>
     </row>
     <row r="151">
@@ -7975,10 +7975,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7206</v>
+        <v>-0.6702</v>
       </c>
       <c r="J151" t="n">
-        <v>-21.618</v>
+        <v>-20.106</v>
       </c>
     </row>
     <row r="152">
@@ -8015,10 +8015,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4277</v>
+        <v>1.2727</v>
       </c>
       <c r="J152" t="n">
-        <v>41.4033</v>
+        <v>36.9083</v>
       </c>
     </row>
     <row r="153">
@@ -8055,10 +8055,10 @@
         <v>1.19</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5567</v>
       </c>
       <c r="J153" t="n">
-        <v>16.7649</v>
+        <v>16.1443</v>
       </c>
     </row>
     <row r="154">
@@ -8095,10 +8095,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1327</v>
+        <v>0.1757</v>
       </c>
       <c r="J154" t="n">
-        <v>3.8483</v>
+        <v>5.0953</v>
       </c>
     </row>
     <row r="155">
@@ -8135,10 +8135,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4153</v>
+        <v>-0.3491</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.0437</v>
+        <v>-10.1239</v>
       </c>
     </row>
     <row r="156">
@@ -8175,10 +8175,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7279</v>
+        <v>-0.6767</v>
       </c>
       <c r="J156" t="n">
-        <v>-21.1091</v>
+        <v>-19.6243</v>
       </c>
     </row>
     <row r="157">
@@ -8215,10 +8215,10 @@
         <v>1.41</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6533</v>
+        <v>0.7984</v>
       </c>
       <c r="J157" t="n">
-        <v>18.9457</v>
+        <v>23.1536</v>
       </c>
     </row>
     <row r="158">
@@ -8255,10 +8255,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5669</v>
+        <v>0.6806</v>
       </c>
       <c r="J158" t="n">
-        <v>16.4401</v>
+        <v>19.7374</v>
       </c>
     </row>
     <row r="159">
@@ -8295,10 +8295,10 @@
         <v>1.03</v>
       </c>
       <c r="I159" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0896</v>
       </c>
       <c r="J159" t="n">
-        <v>2.4534</v>
+        <v>2.5984</v>
       </c>
     </row>
     <row r="160">
@@ -8335,10 +8335,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3724</v>
+        <v>-0.2306</v>
       </c>
       <c r="J160" t="n">
-        <v>-10.7996</v>
+        <v>-6.6874</v>
       </c>
     </row>
     <row r="161">
@@ -8375,10 +8375,10 @@
         <v>0.48</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7881</v>
+        <v>-0.5384</v>
       </c>
       <c r="J161" t="n">
-        <v>-22.8549</v>
+        <v>-15.6136</v>
       </c>
     </row>
     <row r="162">
@@ -8415,10 +8415,10 @@
         <v>1.22</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4073</v>
+        <v>0.4707</v>
       </c>
       <c r="J162" t="n">
-        <v>12.219</v>
+        <v>14.121</v>
       </c>
     </row>
     <row r="163">
@@ -8455,10 +8455,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3345</v>
+        <v>0.3788</v>
       </c>
       <c r="J163" t="n">
-        <v>10.035</v>
+        <v>11.364</v>
       </c>
     </row>
     <row r="164">
@@ -8495,10 +8495,10 @@
         <v>1.14</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2883</v>
+        <v>0.3219</v>
       </c>
       <c r="J164" t="n">
-        <v>8.648999999999999</v>
+        <v>9.657</v>
       </c>
     </row>
     <row r="165">
@@ -8535,10 +8535,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3868</v>
+        <v>-0.2406</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.604</v>
+        <v>-7.218</v>
       </c>
     </row>
     <row r="166">
@@ -8575,10 +8575,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.47</v>
+        <v>-0.2996</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.1</v>
+        <v>-8.988</v>
       </c>
     </row>
     <row r="167">
@@ -8615,10 +8615,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5399</v>
+        <v>0.6515</v>
       </c>
       <c r="J167" t="n">
-        <v>16.197</v>
+        <v>19.545</v>
       </c>
     </row>
     <row r="168">
@@ -8655,10 +8655,10 @@
         <v>1.31</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5013</v>
+        <v>0.6015</v>
       </c>
       <c r="J168" t="n">
-        <v>15.039</v>
+        <v>18.045</v>
       </c>
     </row>
     <row r="169">
@@ -8695,10 +8695,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1376</v>
+        <v>0.1892</v>
       </c>
       <c r="J169" t="n">
-        <v>4.128</v>
+        <v>5.676</v>
       </c>
     </row>
     <row r="170">
@@ -8735,10 +8735,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1043</v>
+        <v>-0.0455</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.129</v>
+        <v>-1.365</v>
       </c>
     </row>
     <row r="171">
@@ -8775,10 +8775,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.431</v>
+        <v>-0.2697</v>
       </c>
       <c r="J171" t="n">
-        <v>-12.93</v>
+        <v>-8.090999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3701/event_3701_evp_summary.xlsx
+++ b/database/event/3701/event_3701_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4766</v>
+        <v>5.126</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8865</v>
+        <v>1.7657</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8344</v>
+        <v>1.7093</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4766</v>
+        <v>5.126</v>
       </c>
       <c r="F2" t="n">
-        <v>3.782</v>
+        <v>3.4824</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6946</v>
+        <v>1.6436</v>
       </c>
       <c r="H2" t="n">
-        <v>4.9449</v>
+        <v>4.8969</v>
       </c>
       <c r="I2" t="n">
-        <v>5.1482</v>
+        <v>5.0231</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6946</v>
+        <v>1.6436</v>
       </c>
       <c r="K2" t="n">
         <v>134</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8428</v>
+        <v>6.666700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>188</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.287</v>
+        <v>5.0227</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8212</v>
+        <v>1.7302</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7488</v>
+        <v>1.6622</v>
       </c>
       <c r="E3" t="n">
-        <v>5.287</v>
+        <v>5.0227</v>
       </c>
       <c r="F3" t="n">
-        <v>2.899</v>
+        <v>2.5863</v>
       </c>
       <c r="G3" t="n">
-        <v>2.388</v>
+        <v>2.4364</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0061</v>
+        <v>2.9357</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1297</v>
+        <v>3.0113</v>
       </c>
       <c r="J3" t="n">
-        <v>2.388</v>
+        <v>2.4364</v>
       </c>
       <c r="K3" t="n">
         <v>134</v>
@@ -575,7 +575,7 @@
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5177</v>
+        <v>5.447699999999999</v>
       </c>
       <c r="N3" t="n">
         <v>188</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.6165</v>
+        <v>2.5458</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9013</v>
+        <v>0.8769</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5432</v>
+        <v>0.5347</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6165</v>
+        <v>2.5458</v>
       </c>
       <c r="F4" t="n">
-        <v>1.067</v>
+        <v>1.0702</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5495</v>
+        <v>1.4756</v>
       </c>
       <c r="H4" t="n">
-        <v>1.067</v>
+        <v>1.0702</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1109</v>
+        <v>1.0978</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5495</v>
+        <v>1.4756</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6604</v>
+        <v>2.5734</v>
       </c>
       <c r="N4" t="n">
         <v>188</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.597</v>
+        <v>2.3798</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8946</v>
+        <v>0.8198</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5344</v>
+        <v>0.4591</v>
       </c>
       <c r="E5" t="n">
-        <v>2.597</v>
+        <v>2.3798</v>
       </c>
       <c r="F5" t="n">
-        <v>2.597</v>
+        <v>2.3798</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.597</v>
+        <v>2.4836</v>
       </c>
       <c r="I5" t="n">
-        <v>2.597</v>
+        <v>2.4836</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.597</v>
+        <v>2.4836</v>
       </c>
       <c r="N5" t="n">
         <v>129</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.421</v>
+        <v>2.3347</v>
       </c>
       <c r="C6" t="n">
-        <v>0.834</v>
+        <v>0.8042</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4549</v>
+        <v>0.4386</v>
       </c>
       <c r="E6" t="n">
-        <v>2.421</v>
+        <v>2.3347</v>
       </c>
       <c r="F6" t="n">
-        <v>2.421</v>
+        <v>2.3347</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.421</v>
+        <v>2.3851</v>
       </c>
       <c r="I6" t="n">
-        <v>2.421</v>
+        <v>2.3851</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.421</v>
+        <v>2.3851</v>
       </c>
       <c r="N6" t="n">
         <v>138</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.1606</v>
+        <v>2.0594</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7443</v>
+        <v>0.7094</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3374</v>
+        <v>0.3133</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1606</v>
+        <v>2.0594</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1606</v>
+        <v>2.0594</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1606</v>
+        <v>2.0594</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1606</v>
+        <v>2.0594</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.1606</v>
+        <v>2.0594</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.0492</v>
+        <v>1.9366</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7059</v>
+        <v>0.6671</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2871</v>
+        <v>0.2574</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0492</v>
+        <v>1.9366</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0492</v>
+        <v>1.9366</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0492</v>
+        <v>1.9366</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0492</v>
+        <v>1.9366</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0492</v>
+        <v>1.9366</v>
       </c>
       <c r="N8" t="n">
         <v>138</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8575</v>
+        <v>1.776</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6398</v>
+        <v>0.6118</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2006</v>
+        <v>0.1843</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8575</v>
+        <v>1.776</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5005</v>
+        <v>1.4482</v>
       </c>
       <c r="G9" t="n">
-        <v>0.357</v>
+        <v>0.3278</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5005</v>
+        <v>1.4482</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5005</v>
+        <v>1.4482</v>
       </c>
       <c r="J9" t="n">
-        <v>0.357</v>
+        <v>0.3278</v>
       </c>
       <c r="K9" t="n">
         <v>131</v>
@@ -851,7 +851,7 @@
         <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8575</v>
+        <v>1.776</v>
       </c>
       <c r="N9" t="n">
         <v>185</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7434</v>
+        <v>1.5963</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6005</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.149</v>
+        <v>0.1025</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7434</v>
+        <v>1.5963</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7434</v>
+        <v>1.5963</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7434</v>
+        <v>1.5963</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7434</v>
+        <v>1.5963</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.7434</v>
+        <v>1.5963</v>
       </c>
       <c r="N10" t="n">
         <v>142</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5445</v>
+        <v>1.5131</v>
       </c>
       <c r="C11" t="n">
-        <v>0.532</v>
+        <v>0.5212</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0593</v>
+        <v>0.0646</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5445</v>
+        <v>1.5131</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6501</v>
+        <v>0.6453</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8944</v>
+        <v>0.8678</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6501</v>
+        <v>0.6453</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6768</v>
+        <v>0.6619</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8944</v>
+        <v>0.8678</v>
       </c>
       <c r="K11" t="n">
         <v>134</v>
@@ -943,7 +943,7 @@
         <v>54</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5712</v>
+        <v>1.5297</v>
       </c>
       <c r="N11" t="n">
         <v>188</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3918</v>
+        <v>1.3101</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4794</v>
+        <v>0.4513</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0097</v>
+        <v>-0.0278</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3918</v>
+        <v>1.3101</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3918</v>
+        <v>1.3101</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3918</v>
+        <v>1.3101</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3918</v>
+        <v>1.3101</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3918</v>
+        <v>1.3101</v>
       </c>
       <c r="N12" t="n">
         <v>129</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2363</v>
+        <v>1.0954</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4259</v>
+        <v>0.3773</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0799</v>
+        <v>-0.1256</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2363</v>
+        <v>1.0954</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9708</v>
+        <v>1.8524</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7345</v>
+        <v>-0.757</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9708</v>
+        <v>1.8524</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9708</v>
+        <v>1.8524</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7345</v>
+        <v>-0.757</v>
       </c>
       <c r="K13" t="n">
         <v>131</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2363</v>
+        <v>1.0954</v>
       </c>
       <c r="N13" t="n">
         <v>185</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1277</v>
+        <v>1.0037</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3885</v>
+        <v>0.3457</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1289</v>
+        <v>-0.1673</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1277</v>
+        <v>1.0037</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1277</v>
+        <v>1.0037</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1277</v>
+        <v>1.0037</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1277</v>
+        <v>1.0037</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1277</v>
+        <v>1.0037</v>
       </c>
       <c r="N14" t="n">
         <v>132</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9326</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3213</v>
+        <v>0.329</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.217</v>
+        <v>-0.1894</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9326</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9326</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9326</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9326</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9326</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>138</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8941</v>
+        <v>0.8615</v>
       </c>
       <c r="C16" t="n">
-        <v>0.308</v>
+        <v>0.2968</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2344</v>
+        <v>-0.232</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8941</v>
+        <v>0.8615</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8941</v>
+        <v>0.8615</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8941</v>
+        <v>0.8615</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8941</v>
+        <v>0.8615</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8941</v>
+        <v>0.8615</v>
       </c>
       <c r="N16" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.867</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2987</v>
+        <v>0.2887</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2466</v>
+        <v>-0.2426</v>
       </c>
       <c r="E17" t="n">
-        <v>0.867</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.867</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.867</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.867</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.867</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7912</v>
+        <v>0.7594</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2725</v>
+        <v>0.2616</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2808</v>
+        <v>-0.2785</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7912</v>
+        <v>0.7594</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7912</v>
+        <v>0.7594</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7912</v>
+        <v>0.7594</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7912</v>
+        <v>0.7594</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7912</v>
+        <v>0.7594</v>
       </c>
       <c r="N18" t="n">
         <v>84</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.734</v>
+        <v>0.669</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2528</v>
+        <v>0.2304</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3066</v>
+        <v>-0.3197</v>
       </c>
       <c r="E19" t="n">
-        <v>0.734</v>
+        <v>0.669</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2074</v>
+        <v>1.1707</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4734</v>
+        <v>-0.5017</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2074</v>
+        <v>1.1707</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2074</v>
+        <v>1.1707</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4734</v>
+        <v>-0.5017</v>
       </c>
       <c r="K19" t="n">
         <v>131</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.734</v>
+        <v>0.669</v>
       </c>
       <c r="N19" t="n">
         <v>185</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7056</v>
+        <v>0.6636</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2431</v>
+        <v>0.2286</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3195</v>
+        <v>-0.3221</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7056</v>
+        <v>0.6636</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0227</v>
+        <v>0.6636</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3171</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0227</v>
+        <v>0.6636</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0227</v>
+        <v>0.6636</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3171</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7056</v>
+        <v>0.6636</v>
       </c>
       <c r="N20" t="n">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6694</v>
+        <v>0.6191</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2306</v>
+        <v>0.2133</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3358</v>
+        <v>-0.3424</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6694</v>
+        <v>0.6191</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6694</v>
+        <v>0.9722</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.3531</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6694</v>
+        <v>0.9722</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6694</v>
+        <v>0.9722</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.3531</v>
       </c>
       <c r="K21" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6694</v>
+        <v>0.6191</v>
       </c>
       <c r="N21" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2009</v>
+        <v>0.1817</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3747</v>
+        <v>-0.3841</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5274</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4584</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1741</v>
+        <v>0.1579</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4098</v>
+        <v>-0.4155</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5054999999999999</v>
+        <v>0.4584</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5097</v>
+        <v>0.4807</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0042</v>
+        <v>-0.0223</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5097</v>
+        <v>0.4807</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5097</v>
+        <v>0.4807</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0042</v>
+        <v>-0.0223</v>
       </c>
       <c r="K23" t="n">
         <v>131</v>
@@ -1495,7 +1495,7 @@
         <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5055000000000001</v>
+        <v>0.4584</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3773</v>
+        <v>0.3062</v>
       </c>
       <c r="C24" t="n">
-        <v>0.13</v>
+        <v>0.1055</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4677</v>
+        <v>-0.4848</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3773</v>
+        <v>0.3062</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3773</v>
+        <v>0.3062</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3773</v>
+        <v>0.3062</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3773</v>
+        <v>0.3062</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3773</v>
+        <v>0.3062</v>
       </c>
       <c r="N24" t="n">
         <v>129</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1735</v>
+        <v>0.1313</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0598</v>
+        <v>0.0452</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5597</v>
+        <v>-0.5644</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1735</v>
+        <v>0.1313</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1735</v>
+        <v>0.1313</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1735</v>
+        <v>0.1313</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1735</v>
+        <v>0.1313</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1735</v>
+        <v>0.1313</v>
       </c>
       <c r="N25" t="n">
         <v>132</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0357</v>
+        <v>-0.0103</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0123</v>
+        <v>-0.0035</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6219</v>
+        <v>-0.6289</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0357</v>
+        <v>-0.0103</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0357</v>
+        <v>-0.0103</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0357</v>
+        <v>-0.0103</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0357</v>
+        <v>-0.0103</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0357</v>
+        <v>-0.0103</v>
       </c>
       <c r="N26" t="n">
         <v>138</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0684</v>
+        <v>-0.0674</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0236</v>
+        <v>-0.0232</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6689000000000001</v>
+        <v>-0.6549</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0684</v>
+        <v>-0.0674</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0684</v>
+        <v>-0.0674</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0684</v>
+        <v>-0.0674</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0684</v>
+        <v>-0.0674</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0684</v>
+        <v>-0.0674</v>
       </c>
       <c r="N27" t="n">
         <v>58</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2995</v>
+        <v>-0.3767</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1032</v>
+        <v>-0.1298</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7732</v>
+        <v>-0.7957</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2995</v>
+        <v>-0.3767</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2995</v>
+        <v>-0.3767</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2995</v>
+        <v>-0.3767</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2995</v>
+        <v>-0.3767</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2995</v>
+        <v>-0.3767</v>
       </c>
       <c r="N28" t="n">
         <v>132</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1919</v>
+        <v>-0.2095</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8895</v>
+        <v>-0.9011</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="N29" t="n">
         <v>132</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.0482</v>
+        <v>-1.0616</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3611</v>
+        <v>-0.3657</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1112</v>
+        <v>-1.1075</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0482</v>
+        <v>-1.0616</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.0482</v>
+        <v>-1.0616</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.0482</v>
+        <v>-1.0616</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.0482</v>
+        <v>-1.0616</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.0482</v>
+        <v>-1.0616</v>
       </c>
       <c r="N30" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0528</v>
+        <v>-1.0876</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3627</v>
+        <v>-0.3746</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1133</v>
+        <v>-1.1193</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0528</v>
+        <v>-1.0876</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0528</v>
+        <v>-1.0876</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0528</v>
+        <v>-1.0876</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0528</v>
+        <v>-1.0876</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0528</v>
+        <v>-1.0876</v>
       </c>
       <c r="N31" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.7638</v>
+        <v>-1.6189</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.6076</v>
+        <v>-0.5577</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.4343</v>
+        <v>-1.3612</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.7638</v>
+        <v>-1.6189</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.0233</v>
+        <v>-0.9876</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.7405</v>
+        <v>-0.6313</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.0233</v>
+        <v>-0.9876</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0654</v>
+        <v>-1.0131</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.7405</v>
+        <v>-0.6313</v>
       </c>
       <c r="K32" t="n">
         <v>134</v>
@@ -1909,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.8059</v>
+        <v>-1.6444</v>
       </c>
       <c r="N32" t="n">
         <v>188</v>
@@ -2015,10 +2015,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0785</v>
+        <v>-0.1036</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.041</v>
+        <v>-2.6936</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2055,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.193</v>
+        <v>-0.2168</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.018</v>
+        <v>-5.6368</v>
       </c>
     </row>
     <row r="4">
@@ -2095,10 +2095,10 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3842</v>
+        <v>-0.4019</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.9892</v>
+        <v>-10.4494</v>
       </c>
     </row>
     <row r="5">
@@ -2135,10 +2135,10 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3842</v>
+        <v>-0.4019</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.9892</v>
+        <v>-10.4494</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2175,10 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.5339</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.6422</v>
+        <v>-13.8814</v>
       </c>
     </row>
     <row r="7">
@@ -2215,10 +2215,10 @@
         <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2254</v>
+        <v>1.2716</v>
       </c>
       <c r="J7" t="n">
-        <v>31.8604</v>
+        <v>33.0616</v>
       </c>
     </row>
     <row r="8">
@@ -2255,10 +2255,10 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0686</v>
+        <v>1.0431</v>
       </c>
       <c r="J8" t="n">
-        <v>27.7836</v>
+        <v>27.1206</v>
       </c>
     </row>
     <row r="9">
@@ -2295,10 +2295,10 @@
         <v>1.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0562</v>
+        <v>1.0252</v>
       </c>
       <c r="J9" t="n">
-        <v>27.4612</v>
+        <v>26.6552</v>
       </c>
     </row>
     <row r="10">
@@ -2335,10 +2335,10 @@
         <v>1.32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8022</v>
+        <v>0.7678</v>
       </c>
       <c r="J10" t="n">
-        <v>20.8572</v>
+        <v>19.9628</v>
       </c>
     </row>
     <row r="11">
@@ -2375,10 +2375,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2865</v>
+        <v>0.3054</v>
       </c>
       <c r="J11" t="n">
-        <v>7.449</v>
+        <v>7.9404</v>
       </c>
     </row>
     <row r="12">
@@ -2415,10 +2415,10 @@
         <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4355</v>
+        <v>0.4314</v>
       </c>
       <c r="J12" t="n">
-        <v>12.194</v>
+        <v>12.0792</v>
       </c>
     </row>
     <row r="13">
@@ -2455,10 +2455,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.38</v>
+        <v>0.3796</v>
       </c>
       <c r="J13" t="n">
-        <v>10.64</v>
+        <v>10.6288</v>
       </c>
     </row>
     <row r="14">
@@ -2495,10 +2495,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0892</v>
+        <v>-0.0998</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4976</v>
+        <v>-2.7944</v>
       </c>
     </row>
     <row r="15">
@@ -2535,10 +2535,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1241</v>
+        <v>-0.1363</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.4748</v>
+        <v>-3.8164</v>
       </c>
     </row>
     <row r="16">
@@ -2575,10 +2575,10 @@
         <v>0.83</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2098</v>
+        <v>-0.2231</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.8744</v>
+        <v>-6.2468</v>
       </c>
     </row>
     <row r="17">
@@ -2615,10 +2615,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1626</v>
+        <v>1.1648</v>
       </c>
       <c r="J17" t="n">
-        <v>32.5528</v>
+        <v>32.6144</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2655,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7473</v>
+        <v>0.7078</v>
       </c>
       <c r="J18" t="n">
-        <v>20.9244</v>
+        <v>19.8184</v>
       </c>
     </row>
     <row r="19">
@@ -2695,10 +2695,10 @@
         <v>1.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.626</v>
+        <v>0.6005</v>
       </c>
       <c r="J19" t="n">
-        <v>17.528</v>
+        <v>16.814</v>
       </c>
     </row>
     <row r="20">
@@ -2735,10 +2735,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1618</v>
+        <v>-0.1574</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.5304</v>
+        <v>-4.4072</v>
       </c>
     </row>
     <row r="21">
@@ -2775,10 +2775,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.027</v>
+        <v>-0.9367</v>
       </c>
       <c r="J21" t="n">
-        <v>-28.756</v>
+        <v>-26.2276</v>
       </c>
     </row>
     <row r="22">
@@ -2815,10 +2815,10 @@
         <v>1.24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5059</v>
+        <v>0.4967</v>
       </c>
       <c r="J22" t="n">
-        <v>15.177</v>
+        <v>14.901</v>
       </c>
     </row>
     <row r="23">
@@ -2855,10 +2855,10 @@
         <v>1.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4519</v>
+        <v>0.447</v>
       </c>
       <c r="J23" t="n">
-        <v>13.557</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="24">
@@ -2895,10 +2895,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.136</v>
+        <v>-0.1483</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.08</v>
+        <v>-4.449</v>
       </c>
     </row>
     <row r="25">
@@ -2935,10 +2935,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1687</v>
+        <v>-0.1816</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.061</v>
+        <v>-5.448</v>
       </c>
     </row>
     <row r="26">
@@ -2975,10 +2975,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1793</v>
+        <v>-0.1923</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.379</v>
+        <v>-5.769</v>
       </c>
     </row>
     <row r="27">
@@ -3015,10 +3015,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9091</v>
+        <v>0.8462</v>
       </c>
       <c r="J27" t="n">
-        <v>27.273</v>
+        <v>25.386</v>
       </c>
     </row>
     <row r="28">
@@ -3055,10 +3055,10 @@
         <v>1.08</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2713</v>
+        <v>0.2748</v>
       </c>
       <c r="J28" t="n">
-        <v>8.138999999999999</v>
+        <v>8.244</v>
       </c>
     </row>
     <row r="29">
@@ -3095,10 +3095,10 @@
         <v>1.06</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2133</v>
+        <v>0.2198</v>
       </c>
       <c r="J29" t="n">
-        <v>6.399</v>
+        <v>6.594</v>
       </c>
     </row>
     <row r="30">
@@ -3135,10 +3135,10 @@
         <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0383</v>
+        <v>0.0485</v>
       </c>
       <c r="J30" t="n">
-        <v>1.149</v>
+        <v>1.455</v>
       </c>
     </row>
     <row r="31">
@@ -3175,10 +3175,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3988</v>
+        <v>-0.383</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.964</v>
+        <v>-11.49</v>
       </c>
     </row>
     <row r="32">
@@ -3215,10 +3215,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9196</v>
+        <v>0.8657</v>
       </c>
       <c r="J32" t="n">
-        <v>23.9096</v>
+        <v>22.5082</v>
       </c>
     </row>
     <row r="33">
@@ -3255,10 +3255,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8756</v>
+        <v>0.8266</v>
       </c>
       <c r="J33" t="n">
-        <v>22.7656</v>
+        <v>21.4916</v>
       </c>
     </row>
     <row r="34">
@@ -3295,10 +3295,10 @@
         <v>1.3</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7853</v>
+        <v>0.7473</v>
       </c>
       <c r="J34" t="n">
-        <v>20.4178</v>
+        <v>19.4298</v>
       </c>
     </row>
     <row r="35">
@@ -3335,10 +3335,10 @@
         <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.295</v>
+        <v>0.305</v>
       </c>
       <c r="J35" t="n">
-        <v>7.67</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="36">
@@ -3375,10 +3375,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1763</v>
+        <v>0.1943</v>
       </c>
       <c r="J36" t="n">
-        <v>4.5838</v>
+        <v>5.0518</v>
       </c>
     </row>
     <row r="37">
@@ -3415,10 +3415,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4765</v>
+        <v>0.458</v>
       </c>
       <c r="J37" t="n">
-        <v>12.389</v>
+        <v>11.908</v>
       </c>
     </row>
     <row r="38">
@@ -3455,10 +3455,10 @@
         <v>0.84</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1822</v>
+        <v>-0.1994</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.7372</v>
+        <v>-5.1844</v>
       </c>
     </row>
     <row r="39">
@@ -3495,10 +3495,10 @@
         <v>0.83</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1921</v>
+        <v>-0.2094</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.9946</v>
+        <v>-5.4444</v>
       </c>
     </row>
     <row r="40">
@@ -3535,10 +3535,10 @@
         <v>0.73</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2901</v>
+        <v>-0.3062</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.5426</v>
+        <v>-7.9612</v>
       </c>
     </row>
     <row r="41">
@@ -3575,10 +3575,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3093</v>
+        <v>-0.3248</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.0418</v>
+        <v>-8.444800000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3615,10 +3615,10 @@
         <v>1.53</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1601</v>
+        <v>1.1279</v>
       </c>
       <c r="J42" t="n">
-        <v>26.6823</v>
+        <v>25.9417</v>
       </c>
     </row>
     <row r="43">
@@ -3655,10 +3655,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9665</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>22.2295</v>
+        <v>20.9944</v>
       </c>
     </row>
     <row r="44">
@@ -3695,10 +3695,10 @@
         <v>1.29</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7528</v>
+        <v>0.7206</v>
       </c>
       <c r="J44" t="n">
-        <v>17.3144</v>
+        <v>16.5738</v>
       </c>
     </row>
     <row r="45">
@@ -3735,10 +3735,10 @@
         <v>1.18</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4949</v>
+        <v>0.49</v>
       </c>
       <c r="J45" t="n">
-        <v>11.3827</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="46">
@@ -3775,10 +3775,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0984</v>
+        <v>0.1233</v>
       </c>
       <c r="J46" t="n">
-        <v>2.2632</v>
+        <v>2.8359</v>
       </c>
     </row>
     <row r="47">
@@ -3815,10 +3815,10 @@
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1645</v>
+        <v>0.1599</v>
       </c>
       <c r="J47" t="n">
-        <v>3.7835</v>
+        <v>3.6777</v>
       </c>
     </row>
     <row r="48">
@@ -3855,10 +3855,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0413</v>
+        <v>0.0299</v>
       </c>
       <c r="J48" t="n">
-        <v>0.9499</v>
+        <v>0.6877</v>
       </c>
     </row>
     <row r="49">
@@ -3895,10 +3895,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1805</v>
+        <v>-0.1981</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.1515</v>
+        <v>-4.5563</v>
       </c>
     </row>
     <row r="50">
@@ -3935,10 +3935,10 @@
         <v>0.75</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2679</v>
+        <v>-0.285</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.1617</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="51">
@@ -3975,10 +3975,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4471</v>
+        <v>-0.4573</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.2833</v>
+        <v>-10.5179</v>
       </c>
     </row>
     <row r="52">
@@ -4015,10 +4015,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0307</v>
+        <v>0.9755</v>
       </c>
       <c r="J52" t="n">
-        <v>30.921</v>
+        <v>29.265</v>
       </c>
     </row>
     <row r="53">
@@ -4055,10 +4055,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7809</v>
+        <v>0.7399</v>
       </c>
       <c r="J53" t="n">
-        <v>23.427</v>
+        <v>22.197</v>
       </c>
     </row>
     <row r="54">
@@ -4095,10 +4095,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5174</v>
+        <v>0.5053</v>
       </c>
       <c r="J54" t="n">
-        <v>15.522</v>
+        <v>15.159</v>
       </c>
     </row>
     <row r="55">
@@ -4135,10 +4135,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0564</v>
+        <v>0.074</v>
       </c>
       <c r="J55" t="n">
-        <v>1.692</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="56">
@@ -4175,10 +4175,10 @@
         <v>0.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3352</v>
+        <v>-0.3191</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.056</v>
+        <v>-9.573</v>
       </c>
     </row>
     <row r="57">
@@ -4215,10 +4215,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6737</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>20.211</v>
+        <v>19.521</v>
       </c>
     </row>
     <row r="58">
@@ -4255,10 +4255,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2981</v>
+        <v>0.3037</v>
       </c>
       <c r="J58" t="n">
-        <v>8.943</v>
+        <v>9.111000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -4295,10 +4295,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2188</v>
+        <v>0.2276</v>
       </c>
       <c r="J59" t="n">
-        <v>6.564</v>
+        <v>6.828</v>
       </c>
     </row>
     <row r="60">
@@ -4335,10 +4335,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1378</v>
+        <v>-0.1497</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.134</v>
+        <v>-4.491</v>
       </c>
     </row>
     <row r="61">
@@ -4375,10 +4375,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3398</v>
+        <v>-0.3504</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.194</v>
+        <v>-10.512</v>
       </c>
     </row>
     <row r="62">
@@ -4415,10 +4415,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.48</v>
+        <v>0.4496</v>
       </c>
       <c r="J62" t="n">
-        <v>11.04</v>
+        <v>10.3408</v>
       </c>
     </row>
     <row r="63">
@@ -4455,10 +4455,10 @@
         <v>0.76</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2485</v>
+        <v>-0.2681</v>
       </c>
       <c r="J63" t="n">
-        <v>-5.7155</v>
+        <v>-6.1663</v>
       </c>
     </row>
     <row r="64">
@@ -4495,10 +4495,10 @@
         <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3319</v>
+        <v>-0.3495</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.6337</v>
+        <v>-8.038500000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4535,10 +4535,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3319</v>
+        <v>-0.3495</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.6337</v>
+        <v>-8.038500000000001</v>
       </c>
     </row>
     <row r="66">
@@ -4575,10 +4575,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4907</v>
+        <v>-0.5003</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.2861</v>
+        <v>-11.5069</v>
       </c>
     </row>
     <row r="67">
@@ -4615,10 +4615,10 @@
         <v>1.76</v>
       </c>
       <c r="I67" t="n">
-        <v>1.4096</v>
+        <v>1.3986</v>
       </c>
       <c r="J67" t="n">
-        <v>32.4208</v>
+        <v>32.1678</v>
       </c>
     </row>
     <row r="68">
@@ -4655,10 +4655,10 @@
         <v>1.5</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1023</v>
+        <v>1.0697</v>
       </c>
       <c r="J68" t="n">
-        <v>25.3529</v>
+        <v>24.6031</v>
       </c>
     </row>
     <row r="69">
@@ -4695,10 +4695,10 @@
         <v>1.42</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9978</v>
+        <v>0.9497</v>
       </c>
       <c r="J69" t="n">
-        <v>22.9494</v>
+        <v>21.8431</v>
       </c>
     </row>
     <row r="70">
@@ -4735,10 +4735,10 @@
         <v>1.22</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5593</v>
       </c>
       <c r="J70" t="n">
-        <v>13.018</v>
+        <v>12.8639</v>
       </c>
     </row>
     <row r="71">
@@ -4775,10 +4775,10 @@
         <v>1.17</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4416</v>
+        <v>0.4476</v>
       </c>
       <c r="J71" t="n">
-        <v>10.1568</v>
+        <v>10.2948</v>
       </c>
     </row>
     <row r="72">
@@ -4815,10 +4815,10 @@
         <v>1.42</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8335</v>
+        <v>0.7902</v>
       </c>
       <c r="J72" t="n">
-        <v>20.8375</v>
+        <v>19.755</v>
       </c>
     </row>
     <row r="73">
@@ -4855,10 +4855,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.573</v>
       </c>
       <c r="J73" t="n">
-        <v>14.805</v>
+        <v>14.325</v>
       </c>
     </row>
     <row r="74">
@@ -4895,10 +4895,10 @@
         <v>0.82</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2158</v>
+        <v>-0.23</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.395</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="75">
@@ -4935,10 +4935,10 @@
         <v>0.76</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2755</v>
+        <v>-0.289</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.8875</v>
+        <v>-7.225</v>
       </c>
     </row>
     <row r="76">
@@ -4975,10 +4975,10 @@
         <v>0.59</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4356</v>
+        <v>-0.4438</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.89</v>
+        <v>-11.095</v>
       </c>
     </row>
     <row r="77">
@@ -5015,10 +5015,10 @@
         <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5996</v>
+        <v>0.5724</v>
       </c>
       <c r="J77" t="n">
-        <v>14.99</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="78">
@@ -5055,10 +5055,10 @@
         <v>1.12</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3884</v>
+        <v>0.382</v>
       </c>
       <c r="J78" t="n">
-        <v>9.710000000000001</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -5095,10 +5095,10 @@
         <v>1.03</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1205</v>
+        <v>0.129</v>
       </c>
       <c r="J79" t="n">
-        <v>3.0125</v>
+        <v>3.225</v>
       </c>
     </row>
     <row r="80">
@@ -5135,10 +5135,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0653</v>
+        <v>-0.0668</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.6325</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="81">
@@ -5175,10 +5175,10 @@
         <v>0.92</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3048</v>
+        <v>-0.2978</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.62</v>
+        <v>-7.445</v>
       </c>
     </row>
     <row r="82">
@@ -5215,10 +5215,10 @@
         <v>1.9</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6119</v>
+        <v>1.6049</v>
       </c>
       <c r="J82" t="n">
-        <v>40.2975</v>
+        <v>40.1225</v>
       </c>
     </row>
     <row r="83">
@@ -5255,10 +5255,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6435</v>
+        <v>0.6224</v>
       </c>
       <c r="J83" t="n">
-        <v>16.0875</v>
+        <v>15.56</v>
       </c>
     </row>
     <row r="84">
@@ -5295,10 +5295,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5151</v>
       </c>
       <c r="J84" t="n">
-        <v>13.0925</v>
+        <v>12.8775</v>
       </c>
     </row>
     <row r="85">
@@ -5335,10 +5335,10 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4736</v>
+        <v>0.4699</v>
       </c>
       <c r="J85" t="n">
-        <v>11.84</v>
+        <v>11.7475</v>
       </c>
     </row>
     <row r="86">
@@ -5375,10 +5375,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5859</v>
+        <v>-0.5427</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.6475</v>
+        <v>-13.5675</v>
       </c>
     </row>
     <row r="87">
@@ -5415,10 +5415,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3948</v>
+        <v>0.3747</v>
       </c>
       <c r="J87" t="n">
-        <v>9.869999999999999</v>
+        <v>9.3675</v>
       </c>
     </row>
     <row r="88">
@@ -5455,10 +5455,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2047</v>
+        <v>-0.2237</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.1175</v>
+        <v>-5.5925</v>
       </c>
     </row>
     <row r="89">
@@ -5495,10 +5495,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2238</v>
+        <v>-0.2428</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.595</v>
+        <v>-6.07</v>
       </c>
     </row>
     <row r="90">
@@ -5535,10 +5535,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3746</v>
+        <v>-0.3895</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.365</v>
+        <v>-9.737500000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5575,10 +5575,10 @@
         <v>0.57</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4307</v>
+        <v>-0.4429</v>
       </c>
       <c r="J91" t="n">
-        <v>-10.7675</v>
+        <v>-11.0725</v>
       </c>
     </row>
     <row r="92">
@@ -5615,10 +5615,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9034</v>
       </c>
       <c r="J92" t="n">
-        <v>27.9618</v>
+        <v>26.1986</v>
       </c>
     </row>
     <row r="93">
@@ -5655,10 +5655,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6653</v>
+        <v>0.6373</v>
       </c>
       <c r="J93" t="n">
-        <v>19.2937</v>
+        <v>18.4817</v>
       </c>
     </row>
     <row r="94">
@@ -5695,10 +5695,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
       <c r="J94" t="n">
-        <v>10.6633</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="95">
@@ -5735,10 +5735,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3677</v>
+        <v>0.368</v>
       </c>
       <c r="J95" t="n">
-        <v>10.6633</v>
+        <v>10.672</v>
       </c>
     </row>
     <row r="96">
@@ -5775,10 +5775,10 @@
         <v>0.92</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3326</v>
+        <v>-0.3173</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.6454</v>
+        <v>-9.201700000000001</v>
       </c>
     </row>
     <row r="97">
@@ -5815,10 +5815,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9671</v>
+        <v>0.9032</v>
       </c>
       <c r="J97" t="n">
-        <v>28.0459</v>
+        <v>26.1928</v>
       </c>
     </row>
     <row r="98">
@@ -5855,10 +5855,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0347</v>
+        <v>0.0251</v>
       </c>
       <c r="J98" t="n">
-        <v>1.0063</v>
+        <v>0.7279</v>
       </c>
     </row>
     <row r="99">
@@ -5895,10 +5895,10 @@
         <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2508</v>
+        <v>-0.2678</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.2732</v>
+        <v>-7.7662</v>
       </c>
     </row>
     <row r="100">
@@ -5935,10 +5935,10 @@
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4402</v>
+        <v>-0.4504</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.7658</v>
+        <v>-13.0616</v>
       </c>
     </row>
     <row r="101">
@@ -5975,10 +5975,10 @@
         <v>0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5226</v>
+        <v>-0.5282</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.1554</v>
+        <v>-15.3178</v>
       </c>
     </row>
     <row r="102">
@@ -6015,10 +6015,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1524</v>
+        <v>1.1212</v>
       </c>
       <c r="J102" t="n">
-        <v>23.048</v>
+        <v>22.424</v>
       </c>
     </row>
     <row r="103">
@@ -6055,10 +6055,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7915</v>
+        <v>0.756</v>
       </c>
       <c r="J103" t="n">
-        <v>15.83</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="104">
@@ -6095,10 +6095,10 @@
         <v>1.28</v>
       </c>
       <c r="I104" t="n">
-        <v>0.7248</v>
+        <v>0.697</v>
       </c>
       <c r="J104" t="n">
-        <v>14.496</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="105">
@@ -6135,10 +6135,10 @@
         <v>1.28</v>
       </c>
       <c r="I105" t="n">
-        <v>0.7248</v>
+        <v>0.697</v>
       </c>
       <c r="J105" t="n">
-        <v>14.496</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="106">
@@ -6175,10 +6175,10 @@
         <v>1.23</v>
       </c>
       <c r="I106" t="n">
-        <v>0.6087</v>
+        <v>0.5937</v>
       </c>
       <c r="J106" t="n">
-        <v>12.174</v>
+        <v>11.874</v>
       </c>
     </row>
     <row r="107">
@@ -6215,10 +6215,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4828</v>
+        <v>0.4517</v>
       </c>
       <c r="J107" t="n">
-        <v>9.656000000000001</v>
+        <v>9.034000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6255,10 +6255,10 @@
         <v>0.85</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.157</v>
+        <v>-0.1776</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.14</v>
+        <v>-3.552</v>
       </c>
     </row>
     <row r="109">
@@ -6295,10 +6295,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2661</v>
+        <v>-0.2857</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.322</v>
+        <v>-5.714</v>
       </c>
     </row>
     <row r="110">
@@ -6335,10 +6335,10 @@
         <v>0.5</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4902</v>
+        <v>-0.4999</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.804</v>
+        <v>-9.997999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6375,10 +6375,10 @@
         <v>0.49</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4994</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.988</v>
+        <v>-10.172</v>
       </c>
     </row>
     <row r="112">
@@ -6415,10 +6415,10 @@
         <v>1.37</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9623</v>
+        <v>0.9018</v>
       </c>
       <c r="J112" t="n">
-        <v>27.9067</v>
+        <v>26.1522</v>
       </c>
     </row>
     <row r="113">
@@ -6455,10 +6455,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4692</v>
+        <v>0.4613</v>
       </c>
       <c r="J113" t="n">
-        <v>13.6068</v>
+        <v>13.3777</v>
       </c>
     </row>
     <row r="114">
@@ -6495,10 +6495,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3394</v>
+        <v>0.3422</v>
       </c>
       <c r="J114" t="n">
-        <v>9.842599999999999</v>
+        <v>9.9238</v>
       </c>
     </row>
     <row r="115">
@@ -6535,10 +6535,10 @@
         <v>1.11</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3394</v>
+        <v>0.3422</v>
       </c>
       <c r="J115" t="n">
-        <v>9.842599999999999</v>
+        <v>9.9238</v>
       </c>
     </row>
     <row r="116">
@@ -6575,10 +6575,10 @@
         <v>1.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1622</v>
+        <v>0.1763</v>
       </c>
       <c r="J116" t="n">
-        <v>4.7038</v>
+        <v>5.1127</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5891</v>
+        <v>0.5644</v>
       </c>
       <c r="J117" t="n">
-        <v>17.0839</v>
+        <v>16.3676</v>
       </c>
     </row>
     <row r="118">
@@ -6655,10 +6655,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0669</v>
+        <v>-0.07920000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.9401</v>
+        <v>-2.2968</v>
       </c>
     </row>
     <row r="119">
@@ -6695,10 +6695,10 @@
         <v>0.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0911</v>
+        <v>-0.1047</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.6419</v>
+        <v>-3.0363</v>
       </c>
     </row>
     <row r="120">
@@ -6735,10 +6735,10 @@
         <v>0.77</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2565</v>
+        <v>-0.2722</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.4385</v>
+        <v>-7.8938</v>
       </c>
     </row>
     <row r="121">
@@ -6775,10 +6775,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4272</v>
+        <v>-0.4372</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.3888</v>
+        <v>-12.6788</v>
       </c>
     </row>
     <row r="122">
@@ -6815,10 +6815,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4616</v>
+        <v>0.4575</v>
       </c>
       <c r="J122" t="n">
-        <v>13.848</v>
+        <v>13.725</v>
       </c>
     </row>
     <row r="123">
@@ -6855,10 +6855,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3707</v>
+        <v>0.3729</v>
       </c>
       <c r="J123" t="n">
-        <v>11.121</v>
+        <v>11.187</v>
       </c>
     </row>
     <row r="124">
@@ -6895,10 +6895,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1539</v>
+        <v>0.1645</v>
       </c>
       <c r="J124" t="n">
-        <v>4.617</v>
+        <v>4.935</v>
       </c>
     </row>
     <row r="125">
@@ -6935,10 +6935,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1099</v>
+        <v>0.1203</v>
       </c>
       <c r="J125" t="n">
-        <v>3.297</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="126">
@@ -6975,10 +6975,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3125</v>
+        <v>-0.3237</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.375</v>
+        <v>-9.711</v>
       </c>
     </row>
     <row r="127">
@@ -7015,10 +7015,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9164</v>
+        <v>0.8515</v>
       </c>
       <c r="J127" t="n">
-        <v>27.492</v>
+        <v>25.545</v>
       </c>
     </row>
     <row r="128">
@@ -7055,10 +7055,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2451</v>
+        <v>0.2494</v>
       </c>
       <c r="J128" t="n">
-        <v>7.353</v>
+        <v>7.482</v>
       </c>
     </row>
     <row r="129">
@@ -7095,10 +7095,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1192</v>
+        <v>0.1282</v>
       </c>
       <c r="J129" t="n">
-        <v>3.576</v>
+        <v>3.846</v>
       </c>
     </row>
     <row r="130">
@@ -7135,10 +7135,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1192</v>
+        <v>0.1282</v>
       </c>
       <c r="J130" t="n">
-        <v>3.576</v>
+        <v>3.846</v>
       </c>
     </row>
     <row r="131">
@@ -7175,10 +7175,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5592</v>
+        <v>-0.529</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.776</v>
+        <v>-15.87</v>
       </c>
     </row>
     <row r="132">
@@ -7215,10 +7215,10 @@
         <v>1.65</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3512</v>
+        <v>1.3241</v>
       </c>
       <c r="J132" t="n">
-        <v>32.4288</v>
+        <v>31.7784</v>
       </c>
     </row>
     <row r="133">
@@ -7255,10 +7255,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4477</v>
+        <v>0.4407</v>
       </c>
       <c r="J133" t="n">
-        <v>10.7448</v>
+        <v>10.5768</v>
       </c>
     </row>
     <row r="134">
@@ -7295,10 +7295,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0322</v>
+        <v>-0.0222</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.7728</v>
+        <v>-0.5328000000000001</v>
       </c>
     </row>
     <row r="135">
@@ -7335,10 +7335,10 @@
         <v>0.96</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2005</v>
+        <v>-0.1938</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.812</v>
+        <v>-4.6512</v>
       </c>
     </row>
     <row r="136">
@@ -7375,10 +7375,10 @@
         <v>0.92</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3279</v>
+        <v>-0.3139</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.8696</v>
+        <v>-7.5336</v>
       </c>
     </row>
     <row r="137">
@@ -7415,10 +7415,10 @@
         <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6378</v>
+        <v>0.6126</v>
       </c>
       <c r="J137" t="n">
-        <v>15.3072</v>
+        <v>14.7024</v>
       </c>
     </row>
     <row r="138">
@@ -7455,10 +7455,10 @@
         <v>1.24</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5301</v>
+        <v>0.5145</v>
       </c>
       <c r="J138" t="n">
-        <v>12.7224</v>
+        <v>12.348</v>
       </c>
     </row>
     <row r="139">
@@ -7495,10 +7495,10 @@
         <v>0.78</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2529</v>
+        <v>-0.2674</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.0696</v>
+        <v>-6.4176</v>
       </c>
     </row>
     <row r="140">
@@ -7535,10 +7535,10 @@
         <v>0.72</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3113</v>
+        <v>-0.3246</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.4712</v>
+        <v>-7.7904</v>
       </c>
     </row>
     <row r="141">
@@ -7575,10 +7575,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3209</v>
+        <v>-0.3339</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.7016</v>
+        <v>-8.0136</v>
       </c>
     </row>
     <row r="142">
@@ -7615,10 +7615,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9458</v>
+        <v>0.8948</v>
       </c>
       <c r="J142" t="n">
-        <v>28.374</v>
+        <v>26.844</v>
       </c>
     </row>
     <row r="143">
@@ -7655,10 +7655,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2641</v>
+        <v>0.2701</v>
       </c>
       <c r="J143" t="n">
-        <v>7.923</v>
+        <v>8.103</v>
       </c>
     </row>
     <row r="144">
@@ -7695,10 +7695,10 @@
         <v>0.98</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0368</v>
+        <v>-0.0434</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.104</v>
+        <v>-1.302</v>
       </c>
     </row>
     <row r="145">
@@ -7735,10 +7735,10 @@
         <v>0.73</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3087</v>
+        <v>-0.3207</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.260999999999999</v>
+        <v>-9.621</v>
       </c>
     </row>
     <row r="146">
@@ -7775,10 +7775,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3087</v>
+        <v>-0.3207</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.260999999999999</v>
+        <v>-9.621</v>
       </c>
     </row>
     <row r="147">
@@ -7815,10 +7815,10 @@
         <v>1.59</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2943</v>
+        <v>1.2606</v>
       </c>
       <c r="J147" t="n">
-        <v>38.829</v>
+        <v>37.818</v>
       </c>
     </row>
     <row r="148">
@@ -7855,10 +7855,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2122</v>
+        <v>0.219</v>
       </c>
       <c r="J148" t="n">
-        <v>6.366</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="149">
@@ -7895,10 +7895,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0725</v>
+        <v>-0.0718</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.175</v>
+        <v>-2.154</v>
       </c>
     </row>
     <row r="150">
@@ -7935,10 +7935,10 @@
         <v>0.97</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1506</v>
+        <v>-0.1496</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.518</v>
+        <v>-4.488</v>
       </c>
     </row>
     <row r="151">
@@ -7975,10 +7975,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6702</v>
+        <v>-0.6266</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.106</v>
+        <v>-18.798</v>
       </c>
     </row>
     <row r="152">
@@ -8015,10 +8015,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2727</v>
+        <v>1.2391</v>
       </c>
       <c r="J152" t="n">
-        <v>36.9083</v>
+        <v>35.9339</v>
       </c>
     </row>
     <row r="153">
@@ -8055,10 +8055,10 @@
         <v>1.19</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5567</v>
+        <v>0.5376</v>
       </c>
       <c r="J153" t="n">
-        <v>16.1443</v>
+        <v>15.5904</v>
       </c>
     </row>
     <row r="154">
@@ -8095,10 +8095,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1757</v>
+        <v>0.1857</v>
       </c>
       <c r="J154" t="n">
-        <v>5.0953</v>
+        <v>5.3853</v>
       </c>
     </row>
     <row r="155">
@@ -8135,10 +8135,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3491</v>
+        <v>-0.3355</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.1239</v>
+        <v>-9.7295</v>
       </c>
     </row>
     <row r="156">
@@ -8175,10 +8175,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6767</v>
+        <v>-0.6312</v>
       </c>
       <c r="J156" t="n">
-        <v>-19.6243</v>
+        <v>-18.3048</v>
       </c>
     </row>
     <row r="157">
@@ -8215,10 +8215,10 @@
         <v>1.41</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7984</v>
+        <v>0.7617</v>
       </c>
       <c r="J157" t="n">
-        <v>23.1536</v>
+        <v>22.0893</v>
       </c>
     </row>
     <row r="158">
@@ -8255,10 +8255,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6806</v>
+        <v>0.6558</v>
       </c>
       <c r="J158" t="n">
-        <v>19.7374</v>
+        <v>19.0182</v>
       </c>
     </row>
     <row r="159">
@@ -8295,10 +8295,10 @@
         <v>1.03</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0896</v>
+        <v>0.0984</v>
       </c>
       <c r="J159" t="n">
-        <v>2.5984</v>
+        <v>2.8536</v>
       </c>
     </row>
     <row r="160">
@@ -8335,10 +8335,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2306</v>
+        <v>-0.2437</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.6874</v>
+        <v>-7.0673</v>
       </c>
     </row>
     <row r="161">
@@ -8375,10 +8375,10 @@
         <v>0.48</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5384</v>
+        <v>-0.5407</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.6136</v>
+        <v>-15.6803</v>
       </c>
     </row>
     <row r="162">
@@ -8415,10 +8415,10 @@
         <v>1.22</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4707</v>
+        <v>0.4642</v>
       </c>
       <c r="J162" t="n">
-        <v>14.121</v>
+        <v>13.926</v>
       </c>
     </row>
     <row r="163">
@@ -8495,10 +8495,10 @@
         <v>1.14</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3219</v>
+        <v>0.3253</v>
       </c>
       <c r="J164" t="n">
-        <v>9.657</v>
+        <v>9.759</v>
       </c>
     </row>
     <row r="165">
@@ -8535,10 +8535,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2406</v>
+        <v>-0.2537</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.218</v>
+        <v>-7.611</v>
       </c>
     </row>
     <row r="166">
@@ -8575,10 +8575,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2996</v>
+        <v>-0.3117</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.988</v>
+        <v>-9.351000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -8615,10 +8615,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6515</v>
+        <v>0.6344</v>
       </c>
       <c r="J167" t="n">
-        <v>19.545</v>
+        <v>19.032</v>
       </c>
     </row>
     <row r="168">
@@ -8655,10 +8655,10 @@
         <v>1.31</v>
       </c>
       <c r="I168" t="n">
-        <v>0.6015</v>
+        <v>0.5889</v>
       </c>
       <c r="J168" t="n">
-        <v>18.045</v>
+        <v>17.667</v>
       </c>
     </row>
     <row r="169">
@@ -8695,10 +8695,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.1892</v>
+        <v>0.2012</v>
       </c>
       <c r="J169" t="n">
-        <v>5.676</v>
+        <v>6.036</v>
       </c>
     </row>
     <row r="170">
@@ -8735,10 +8735,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.0455</v>
+        <v>-0.05</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.365</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="171">
@@ -8775,10 +8775,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2697</v>
+        <v>-0.2805</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.090999999999999</v>
+        <v>-8.414999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3701/event_3701_evp_summary.xlsx
+++ b/database/event/3701/event_3701_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.126</v>
+        <v>5.0107</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7657</v>
+        <v>1.726</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7093</v>
+        <v>1.6768</v>
       </c>
       <c r="E2" t="n">
-        <v>5.126</v>
+        <v>5.0107</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4824</v>
+        <v>3.4016</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6436</v>
+        <v>1.6091</v>
       </c>
       <c r="H2" t="n">
-        <v>4.8969</v>
+        <v>4.8454</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0231</v>
+        <v>4.9749</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6436</v>
+        <v>1.6091</v>
       </c>
       <c r="K2" t="n">
         <v>134</v>
@@ -529,7 +529,7 @@
         <v>54</v>
       </c>
       <c r="M2" t="n">
-        <v>6.666700000000001</v>
+        <v>6.584</v>
       </c>
       <c r="N2" t="n">
         <v>188</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0227</v>
+        <v>4.9789</v>
       </c>
       <c r="C3" t="n">
-        <v>1.7302</v>
+        <v>1.7151</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6622</v>
+        <v>1.6623</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0227</v>
+        <v>4.9789</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5863</v>
+        <v>2.5041</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4364</v>
+        <v>2.4748</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9357</v>
+        <v>2.7885</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0113</v>
+        <v>2.863</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4364</v>
+        <v>2.4748</v>
       </c>
       <c r="K3" t="n">
         <v>134</v>
@@ -575,7 +575,7 @@
         <v>54</v>
       </c>
       <c r="M3" t="n">
-        <v>5.447699999999999</v>
+        <v>5.3378</v>
       </c>
       <c r="N3" t="n">
         <v>188</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.5458</v>
+        <v>2.3954</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8769</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5347</v>
+        <v>0.4854</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5458</v>
+        <v>2.3954</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0702</v>
+        <v>0.969</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4756</v>
+        <v>1.4264</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0702</v>
+        <v>0.969</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0978</v>
+        <v>0.9949</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4756</v>
+        <v>1.4264</v>
       </c>
       <c r="K4" t="n">
         <v>134</v>
@@ -621,7 +621,7 @@
         <v>54</v>
       </c>
       <c r="M4" t="n">
-        <v>2.5734</v>
+        <v>2.4213</v>
       </c>
       <c r="N4" t="n">
         <v>188</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.3798</v>
+        <v>2.334</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8198</v>
+        <v>0.804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4591</v>
+        <v>0.4575</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3798</v>
+        <v>2.334</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3798</v>
+        <v>2.334</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4836</v>
+        <v>2.3988</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4836</v>
+        <v>2.3988</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4836</v>
+        <v>2.3988</v>
       </c>
       <c r="N5" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.3347</v>
+        <v>2.331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8042</v>
+        <v>0.803</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4386</v>
+        <v>0.4561</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3347</v>
+        <v>2.331</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3347</v>
+        <v>2.331</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3851</v>
+        <v>2.3919</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3851</v>
+        <v>2.3919</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.3851</v>
+        <v>2.3919</v>
       </c>
       <c r="N6" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.0594</v>
+        <v>1.9026</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7094</v>
+        <v>0.6554</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3133</v>
+        <v>0.2609</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0594</v>
+        <v>1.9026</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0594</v>
+        <v>1.9026</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0594</v>
+        <v>1.9026</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0594</v>
+        <v>1.9026</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.0594</v>
+        <v>1.9026</v>
       </c>
       <c r="N7" t="n">
         <v>142</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.9366</v>
+        <v>1.8601</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6671</v>
+        <v>0.6407</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2574</v>
+        <v>0.2416</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9366</v>
+        <v>1.8601</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9366</v>
+        <v>1.8601</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9366</v>
+        <v>1.8601</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9366</v>
+        <v>1.8601</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9366</v>
+        <v>1.8601</v>
       </c>
       <c r="N8" t="n">
         <v>138</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.776</v>
+        <v>1.6192</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6118</v>
+        <v>0.5578</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1843</v>
+        <v>0.1318</v>
       </c>
       <c r="E9" t="n">
-        <v>1.776</v>
+        <v>1.6192</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4482</v>
+        <v>1.3335</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3278</v>
+        <v>0.2857</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4482</v>
+        <v>1.3335</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4482</v>
+        <v>1.3335</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3278</v>
+        <v>0.2857</v>
       </c>
       <c r="K9" t="n">
         <v>131</v>
@@ -851,7 +851,7 @@
         <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.776</v>
+        <v>1.6192</v>
       </c>
       <c r="N9" t="n">
         <v>185</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.5963</v>
+        <v>1.5112</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5206</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1025</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5963</v>
+        <v>1.5112</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5963</v>
+        <v>0.6112</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5963</v>
+        <v>0.6112</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5963</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K10" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5963</v>
+        <v>1.5275</v>
       </c>
       <c r="N10" t="n">
-        <v>142</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5131</v>
+        <v>1.5016</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5212</v>
+        <v>0.5173</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0646</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5131</v>
+        <v>1.5016</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6453</v>
+        <v>1.5016</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6453</v>
+        <v>1.5016</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6619</v>
+        <v>1.5016</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5297</v>
+        <v>1.5016</v>
       </c>
       <c r="N11" t="n">
-        <v>188</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.3101</v>
+        <v>1.2367</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4513</v>
+        <v>0.426</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0278</v>
+        <v>-0.0424</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3101</v>
+        <v>1.2367</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3101</v>
+        <v>1.2367</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3101</v>
+        <v>1.2367</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3101</v>
+        <v>1.2367</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3101</v>
+        <v>1.2367</v>
       </c>
       <c r="N12" t="n">
         <v>129</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0954</v>
+        <v>1.1076</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3773</v>
+        <v>0.3815</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1256</v>
+        <v>-0.1012</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0954</v>
+        <v>1.1076</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8524</v>
+        <v>1.8465</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.757</v>
+        <v>-0.7389</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8524</v>
+        <v>1.8465</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8524</v>
+        <v>1.8465</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.757</v>
+        <v>-0.7389</v>
       </c>
       <c r="K13" t="n">
         <v>131</v>
@@ -1035,7 +1035,7 @@
         <v>54</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0954</v>
+        <v>1.1076</v>
       </c>
       <c r="N13" t="n">
         <v>185</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0037</v>
+        <v>0.9361</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3457</v>
+        <v>0.3225</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1673</v>
+        <v>-0.1793</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0037</v>
+        <v>0.9361</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0037</v>
+        <v>0.9361</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0037</v>
+        <v>0.9361</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0037</v>
+        <v>0.9361</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0037</v>
+        <v>0.9361</v>
       </c>
       <c r="N14" t="n">
         <v>132</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.8235</v>
       </c>
       <c r="C15" t="n">
-        <v>0.329</v>
+        <v>0.2837</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1894</v>
+        <v>-0.2306</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.8235</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.8235</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.8235</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.8235</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.8235</v>
       </c>
       <c r="N15" t="n">
         <v>138</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8615</v>
+        <v>0.7665</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2968</v>
+        <v>0.264</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.232</v>
+        <v>-0.2566</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8615</v>
+        <v>0.7665</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8615</v>
+        <v>0.7665</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8615</v>
+        <v>0.7665</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8615</v>
+        <v>0.7665</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8615</v>
+        <v>0.7665</v>
       </c>
       <c r="N16" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2887</v>
+        <v>0.2441</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2426</v>
+        <v>-0.2829</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="N17" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7594</v>
+        <v>0.6821</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2616</v>
+        <v>0.235</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2785</v>
+        <v>-0.2951</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7594</v>
+        <v>0.6821</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7594</v>
+        <v>0.6821</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7594</v>
+        <v>0.6821</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7594</v>
+        <v>0.6821</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7594</v>
+        <v>0.6821</v>
       </c>
       <c r="N18" t="n">
         <v>84</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.669</v>
+        <v>0.5828</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2304</v>
+        <v>0.2008</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3197</v>
+        <v>-0.3403</v>
       </c>
       <c r="E19" t="n">
-        <v>0.669</v>
+        <v>0.5828</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1707</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5017</v>
+        <v>-0.3189</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1707</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1707</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5017</v>
+        <v>-0.3189</v>
       </c>
       <c r="K19" t="n">
         <v>131</v>
@@ -1311,7 +1311,7 @@
         <v>54</v>
       </c>
       <c r="M19" t="n">
-        <v>0.669</v>
+        <v>0.5828</v>
       </c>
       <c r="N19" t="n">
         <v>185</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6636</v>
+        <v>0.5821</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2286</v>
+        <v>0.2005</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3221</v>
+        <v>-0.3406</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6636</v>
+        <v>0.5821</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6636</v>
+        <v>1.0567</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.4746</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6636</v>
+        <v>1.0567</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6636</v>
+        <v>1.0567</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.4746</v>
       </c>
       <c r="K20" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6636</v>
+        <v>0.5821</v>
       </c>
       <c r="N20" t="n">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6191</v>
+        <v>0.5714</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2133</v>
+        <v>0.1968</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3424</v>
+        <v>-0.3455</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6191</v>
+        <v>0.5714</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9722</v>
+        <v>0.5714</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3531</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9722</v>
+        <v>0.5714</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9722</v>
+        <v>0.5714</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3531</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6191</v>
+        <v>0.5714</v>
       </c>
       <c r="N21" t="n">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5274</v>
+        <v>0.5128</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1817</v>
+        <v>0.1766</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3841</v>
+        <v>-0.3722</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5274</v>
+        <v>0.5128</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5274</v>
+        <v>0.5128</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5274</v>
+        <v>0.5128</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5274</v>
+        <v>0.5128</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5274</v>
+        <v>0.5128</v>
       </c>
       <c r="N22" t="n">
         <v>142</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4584</v>
+        <v>0.4049</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1579</v>
+        <v>0.1395</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4155</v>
+        <v>-0.4213</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4584</v>
+        <v>0.4049</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4807</v>
+        <v>0.4725</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0223</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4807</v>
+        <v>0.4725</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4807</v>
+        <v>0.4725</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0223</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>131</v>
@@ -1495,7 +1495,7 @@
         <v>54</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4584</v>
+        <v>0.4049</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3062</v>
+        <v>0.306</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1055</v>
+        <v>0.1054</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4848</v>
+        <v>-0.4664</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3062</v>
+        <v>0.306</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3062</v>
+        <v>0.306</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3062</v>
+        <v>0.306</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3062</v>
+        <v>0.306</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3062</v>
+        <v>0.306</v>
       </c>
       <c r="N24" t="n">
         <v>129</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1313</v>
+        <v>0.1091</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0452</v>
+        <v>0.0376</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5644</v>
+        <v>-0.5561</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1313</v>
+        <v>0.1091</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1313</v>
+        <v>0.1091</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1313</v>
+        <v>0.1091</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1313</v>
+        <v>0.1091</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1313</v>
+        <v>0.1091</v>
       </c>
       <c r="N25" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0103</v>
+        <v>0.011</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6289</v>
+        <v>-0.6008</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0103</v>
+        <v>0.011</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0103</v>
+        <v>0.011</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0103</v>
+        <v>0.011</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0103</v>
+        <v>0.011</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0103</v>
+        <v>0.011</v>
       </c>
       <c r="N26" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0674</v>
+        <v>-0.0741</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0232</v>
+        <v>-0.0255</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6549</v>
+        <v>-0.6395</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0674</v>
+        <v>-0.0741</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0674</v>
+        <v>-0.0741</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0674</v>
+        <v>-0.0741</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0674</v>
+        <v>-0.0741</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0674</v>
+        <v>-0.0741</v>
       </c>
       <c r="N27" t="n">
         <v>58</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3767</v>
+        <v>-0.3653</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1298</v>
+        <v>-0.1258</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7957</v>
+        <v>-0.7722</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3767</v>
+        <v>-0.3653</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3767</v>
+        <v>-0.3653</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3767</v>
+        <v>-0.3653</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3767</v>
+        <v>-0.3653</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3767</v>
+        <v>-0.3653</v>
       </c>
       <c r="N28" t="n">
         <v>132</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6083</v>
+        <v>-0.6146</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2095</v>
+        <v>-0.2117</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.9011</v>
+        <v>-0.8858</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6083</v>
+        <v>-0.6146</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6083</v>
+        <v>-0.6146</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6083</v>
+        <v>-0.6146</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6083</v>
+        <v>-0.6146</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6083</v>
+        <v>-0.6146</v>
       </c>
       <c r="N29" t="n">
         <v>132</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.0616</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3657</v>
+        <v>-0.3415</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.1075</v>
+        <v>-1.0574</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.0616</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.0616</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.0616</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.0616</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.0616</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="N30" t="n">
         <v>129</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.0876</v>
+        <v>-1.1021</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3746</v>
+        <v>-0.3796</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.1193</v>
+        <v>-1.1078</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.0876</v>
+        <v>-1.1021</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.0876</v>
+        <v>-1.1021</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.0876</v>
+        <v>-1.1021</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0876</v>
+        <v>-1.1021</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.0876</v>
+        <v>-1.1021</v>
       </c>
       <c r="N31" t="n">
         <v>132</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.6189</v>
+        <v>-1.5387</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.5577</v>
+        <v>-0.53</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.3612</v>
+        <v>-1.3067</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.6189</v>
+        <v>-1.5387</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9876</v>
+        <v>-0.8833</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6313</v>
+        <v>-0.6554</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9876</v>
+        <v>-0.8833</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0131</v>
+        <v>-0.9069</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6313</v>
+        <v>-0.6554</v>
       </c>
       <c r="K32" t="n">
         <v>134</v>
@@ -1909,7 +1909,7 @@
         <v>54</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.6444</v>
+        <v>-1.5623</v>
       </c>
       <c r="N32" t="n">
         <v>188</v>
@@ -2015,10 +2015,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1036</v>
+        <v>-0.0862</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.6936</v>
+        <v>-2.2412</v>
       </c>
     </row>
     <row r="3">
@@ -2055,10 +2055,10 @@
         <v>0.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2168</v>
+        <v>-0.2019</v>
       </c>
       <c r="J3" t="n">
-        <v>-5.6368</v>
+        <v>-5.2494</v>
       </c>
     </row>
     <row r="4">
@@ -2095,10 +2095,10 @@
         <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4019</v>
+        <v>-0.3918</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.4494</v>
+        <v>-10.1868</v>
       </c>
     </row>
     <row r="5">
@@ -2135,10 +2135,10 @@
         <v>0.6</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4019</v>
+        <v>-0.3918</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.4494</v>
+        <v>-10.1868</v>
       </c>
     </row>
     <row r="6">
@@ -2175,10 +2175,10 @@
         <v>0.45</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5339</v>
+        <v>-0.5363</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.8814</v>
+        <v>-13.9438</v>
       </c>
     </row>
     <row r="7">
@@ -2215,10 +2215,10 @@
         <v>1.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2716</v>
+        <v>1.298</v>
       </c>
       <c r="J7" t="n">
-        <v>33.0616</v>
+        <v>33.748</v>
       </c>
     </row>
     <row r="8">
@@ -2255,10 +2255,10 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0431</v>
+        <v>1.0454</v>
       </c>
       <c r="J8" t="n">
-        <v>27.1206</v>
+        <v>27.1804</v>
       </c>
     </row>
     <row r="9">
@@ -2295,10 +2295,10 @@
         <v>1.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0252</v>
+        <v>1.026</v>
       </c>
       <c r="J9" t="n">
-        <v>26.6552</v>
+        <v>26.676</v>
       </c>
     </row>
     <row r="10">
@@ -2335,10 +2335,10 @@
         <v>1.32</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7678</v>
+        <v>0.7508</v>
       </c>
       <c r="J10" t="n">
-        <v>19.9628</v>
+        <v>19.5208</v>
       </c>
     </row>
     <row r="11">
@@ -2375,10 +2375,10 @@
         <v>1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3054</v>
+        <v>0.2732</v>
       </c>
       <c r="J11" t="n">
-        <v>7.9404</v>
+        <v>7.1032</v>
       </c>
     </row>
     <row r="12">
@@ -2415,10 +2415,10 @@
         <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4314</v>
+        <v>0.3739</v>
       </c>
       <c r="J12" t="n">
-        <v>12.0792</v>
+        <v>10.4692</v>
       </c>
     </row>
     <row r="13">
@@ -2455,10 +2455,10 @@
         <v>1.17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3796</v>
+        <v>0.3242</v>
       </c>
       <c r="J13" t="n">
-        <v>10.6288</v>
+        <v>9.0776</v>
       </c>
     </row>
     <row r="14">
@@ -2495,10 +2495,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0998</v>
+        <v>-0.0828</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.7944</v>
+        <v>-2.3184</v>
       </c>
     </row>
     <row r="15">
@@ -2535,10 +2535,10 @@
         <v>0.91</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1363</v>
+        <v>-0.117</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.8164</v>
+        <v>-3.276</v>
       </c>
     </row>
     <row r="16">
@@ -2575,10 +2575,10 @@
         <v>0.83</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2231</v>
+        <v>-0.2026</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.2468</v>
+        <v>-5.6728</v>
       </c>
     </row>
     <row r="17">
@@ -2615,10 +2615,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1648</v>
+        <v>1.1768</v>
       </c>
       <c r="J17" t="n">
-        <v>32.6144</v>
+        <v>32.9504</v>
       </c>
     </row>
     <row r="18">
@@ -2655,10 +2655,10 @@
         <v>1.27</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7078</v>
+        <v>0.6756</v>
       </c>
       <c r="J18" t="n">
-        <v>19.8184</v>
+        <v>18.9168</v>
       </c>
     </row>
     <row r="19">
@@ -2695,10 +2695,10 @@
         <v>1.22</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6005</v>
+        <v>0.5637</v>
       </c>
       <c r="J19" t="n">
-        <v>16.814</v>
+        <v>15.7836</v>
       </c>
     </row>
     <row r="20">
@@ -2735,10 +2735,10 @@
         <v>0.97</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1574</v>
+        <v>-0.126</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.4072</v>
+        <v>-3.528</v>
       </c>
     </row>
     <row r="21">
@@ -2775,10 +2775,10 @@
         <v>0.65</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9367</v>
+        <v>-0.9286</v>
       </c>
       <c r="J21" t="n">
-        <v>-26.2276</v>
+        <v>-26.0008</v>
       </c>
     </row>
     <row r="22">
@@ -2815,10 +2815,10 @@
         <v>1.24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4967</v>
+        <v>0.4377</v>
       </c>
       <c r="J22" t="n">
-        <v>14.901</v>
+        <v>13.131</v>
       </c>
     </row>
     <row r="23">
@@ -2855,10 +2855,10 @@
         <v>1.21</v>
       </c>
       <c r="I23" t="n">
-        <v>0.447</v>
+        <v>0.389</v>
       </c>
       <c r="J23" t="n">
-        <v>13.41</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="24">
@@ -2895,10 +2895,10 @@
         <v>0.9</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1483</v>
+        <v>-0.1285</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.449</v>
+        <v>-3.855</v>
       </c>
     </row>
     <row r="25">
@@ -2935,10 +2935,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1816</v>
+        <v>-0.161</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.448</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="26">
@@ -2975,10 +2975,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1923</v>
+        <v>-0.1717</v>
       </c>
       <c r="J26" t="n">
-        <v>-5.769</v>
+        <v>-5.151</v>
       </c>
     </row>
     <row r="27">
@@ -3015,10 +3015,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8462</v>
+        <v>0.8234</v>
       </c>
       <c r="J27" t="n">
-        <v>25.386</v>
+        <v>24.702</v>
       </c>
     </row>
     <row r="28">
@@ -3055,10 +3055,10 @@
         <v>1.08</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2748</v>
+        <v>0.2387</v>
       </c>
       <c r="J28" t="n">
-        <v>8.244</v>
+        <v>7.161</v>
       </c>
     </row>
     <row r="29">
@@ -3095,10 +3095,10 @@
         <v>1.06</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2198</v>
+        <v>0.1872</v>
       </c>
       <c r="J29" t="n">
-        <v>6.594</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="30">
@@ -3135,10 +3135,10 @@
         <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0485</v>
+        <v>0.0365</v>
       </c>
       <c r="J30" t="n">
-        <v>1.455</v>
+        <v>1.095</v>
       </c>
     </row>
     <row r="31">
@@ -3175,10 +3175,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.383</v>
+        <v>-0.3401</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.49</v>
+        <v>-10.203</v>
       </c>
     </row>
     <row r="32">
@@ -3215,10 +3215,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8657</v>
+        <v>0.8469</v>
       </c>
       <c r="J32" t="n">
-        <v>22.5082</v>
+        <v>22.0194</v>
       </c>
     </row>
     <row r="33">
@@ -3255,10 +3255,10 @@
         <v>1.34</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8266</v>
+        <v>0.8051</v>
       </c>
       <c r="J33" t="n">
-        <v>21.4916</v>
+        <v>20.9326</v>
       </c>
     </row>
     <row r="34">
@@ -3295,10 +3295,10 @@
         <v>1.3</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7473</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>19.4298</v>
+        <v>18.7538</v>
       </c>
     </row>
     <row r="35">
@@ -3335,10 +3335,10 @@
         <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.305</v>
+        <v>0.2729</v>
       </c>
       <c r="J35" t="n">
-        <v>7.93</v>
+        <v>7.0954</v>
       </c>
     </row>
     <row r="36">
@@ -3375,10 +3375,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1943</v>
+        <v>0.1664</v>
       </c>
       <c r="J36" t="n">
-        <v>5.0518</v>
+        <v>4.3264</v>
       </c>
     </row>
     <row r="37">
@@ -3415,10 +3415,10 @@
         <v>1.19</v>
       </c>
       <c r="I37" t="n">
-        <v>0.458</v>
+        <v>0.4046</v>
       </c>
       <c r="J37" t="n">
-        <v>11.908</v>
+        <v>10.5196</v>
       </c>
     </row>
     <row r="38">
@@ -3455,10 +3455,10 @@
         <v>0.84</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1994</v>
+        <v>-0.1807</v>
       </c>
       <c r="J38" t="n">
-        <v>-5.1844</v>
+        <v>-4.6982</v>
       </c>
     </row>
     <row r="39">
@@ -3495,10 +3495,10 @@
         <v>0.83</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2094</v>
+        <v>-0.1905</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.4444</v>
+        <v>-4.953</v>
       </c>
     </row>
     <row r="40">
@@ -3535,10 +3535,10 @@
         <v>0.73</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3062</v>
+        <v>-0.2886</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.9612</v>
+        <v>-7.5036</v>
       </c>
     </row>
     <row r="41">
@@ -3575,10 +3575,10 @@
         <v>0.71</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3248</v>
+        <v>-0.3081</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.444800000000001</v>
+        <v>-8.0106</v>
       </c>
     </row>
     <row r="42">
@@ -3615,10 +3615,10 @@
         <v>1.53</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1279</v>
+        <v>1.1407</v>
       </c>
       <c r="J42" t="n">
-        <v>25.9417</v>
+        <v>26.2361</v>
       </c>
     </row>
     <row r="43">
@@ -3655,10 +3655,10 @@
         <v>1.39</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.8999</v>
       </c>
       <c r="J43" t="n">
-        <v>20.9944</v>
+        <v>20.6977</v>
       </c>
     </row>
     <row r="44">
@@ -3695,10 +3695,10 @@
         <v>1.29</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7206</v>
+        <v>0.6962</v>
       </c>
       <c r="J44" t="n">
-        <v>16.5738</v>
+        <v>16.0126</v>
       </c>
     </row>
     <row r="45">
@@ -3735,10 +3735,10 @@
         <v>1.18</v>
       </c>
       <c r="I45" t="n">
-        <v>0.49</v>
+        <v>0.4587</v>
       </c>
       <c r="J45" t="n">
-        <v>11.27</v>
+        <v>10.5501</v>
       </c>
     </row>
     <row r="46">
@@ -3775,10 +3775,10 @@
         <v>1.04</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1233</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>2.8359</v>
+        <v>2.2885</v>
       </c>
     </row>
     <row r="47">
@@ -3815,10 +3815,10 @@
         <v>1.04</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1599</v>
+        <v>0.1257</v>
       </c>
       <c r="J47" t="n">
-        <v>3.6777</v>
+        <v>2.8911</v>
       </c>
     </row>
     <row r="48">
@@ -3855,10 +3855,10 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0299</v>
+        <v>0.0241</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6877</v>
+        <v>0.5543</v>
       </c>
     </row>
     <row r="49">
@@ -3895,10 +3895,10 @@
         <v>0.84</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1981</v>
+        <v>-0.1801</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.5563</v>
+        <v>-4.1423</v>
       </c>
     </row>
     <row r="50">
@@ -3935,10 +3935,10 @@
         <v>0.75</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.285</v>
+        <v>-0.267</v>
       </c>
       <c r="J50" t="n">
-        <v>-6.555</v>
+        <v>-6.141</v>
       </c>
     </row>
     <row r="51">
@@ -3975,10 +3975,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4573</v>
+        <v>-0.4516</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.5179</v>
+        <v>-10.3868</v>
       </c>
     </row>
     <row r="52">
@@ -4015,10 +4015,10 @@
         <v>1.41</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9755</v>
+        <v>0.9679</v>
       </c>
       <c r="J52" t="n">
-        <v>29.265</v>
+        <v>29.037</v>
       </c>
     </row>
     <row r="53">
@@ -4055,10 +4055,10 @@
         <v>1.29</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7399</v>
+        <v>0.7107</v>
       </c>
       <c r="J53" t="n">
-        <v>22.197</v>
+        <v>21.321</v>
       </c>
     </row>
     <row r="54">
@@ -4095,10 +4095,10 @@
         <v>1.18</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5053</v>
+        <v>0.4689</v>
       </c>
       <c r="J54" t="n">
-        <v>15.159</v>
+        <v>14.067</v>
       </c>
     </row>
     <row r="55">
@@ -4135,10 +4135,10 @@
         <v>1.02</v>
       </c>
       <c r="I55" t="n">
-        <v>0.074</v>
+        <v>0.0575</v>
       </c>
       <c r="J55" t="n">
-        <v>2.22</v>
+        <v>1.725</v>
       </c>
     </row>
     <row r="56">
@@ -4175,10 +4175,10 @@
         <v>0.92</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3191</v>
+        <v>-0.2783</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.573</v>
+        <v>-8.349</v>
       </c>
     </row>
     <row r="57">
@@ -4215,10 +4215,10 @@
         <v>1.34</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="J57" t="n">
-        <v>19.521</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="58">
@@ -4255,10 +4255,10 @@
         <v>1.13</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3037</v>
+        <v>0.2533</v>
       </c>
       <c r="J58" t="n">
-        <v>9.111000000000001</v>
+        <v>7.599</v>
       </c>
     </row>
     <row r="59">
@@ -4295,10 +4295,10 @@
         <v>1.09</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2276</v>
+        <v>0.1843</v>
       </c>
       <c r="J59" t="n">
-        <v>6.828</v>
+        <v>5.529</v>
       </c>
     </row>
     <row r="60">
@@ -4335,10 +4335,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1497</v>
+        <v>-0.1298</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.491</v>
+        <v>-3.894</v>
       </c>
     </row>
     <row r="61">
@@ -4375,10 +4375,10 @@
         <v>0.7</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3504</v>
+        <v>-0.3361</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.512</v>
+        <v>-10.083</v>
       </c>
     </row>
     <row r="62">
@@ -4415,10 +4415,10 @@
         <v>1.16</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4496</v>
+        <v>0.4073</v>
       </c>
       <c r="J62" t="n">
-        <v>10.3408</v>
+        <v>9.367900000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4455,10 +4455,10 @@
         <v>0.76</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2681</v>
+        <v>-0.2522</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.1663</v>
+        <v>-5.8006</v>
       </c>
     </row>
     <row r="64">
@@ -4495,10 +4495,10 @@
         <v>0.67</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3495</v>
+        <v>-0.3351</v>
       </c>
       <c r="J64" t="n">
-        <v>-8.038500000000001</v>
+        <v>-7.7073</v>
       </c>
     </row>
     <row r="65">
@@ -4535,10 +4535,10 @@
         <v>0.67</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3495</v>
+        <v>-0.3351</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.038500000000001</v>
+        <v>-7.7073</v>
       </c>
     </row>
     <row r="66">
@@ -4575,10 +4575,10 @@
         <v>0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5003</v>
+        <v>-0.499</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.5069</v>
+        <v>-11.477</v>
       </c>
     </row>
     <row r="67">
@@ -4615,10 +4615,10 @@
         <v>1.76</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3986</v>
+        <v>1.4235</v>
       </c>
       <c r="J67" t="n">
-        <v>32.1678</v>
+        <v>32.7405</v>
       </c>
     </row>
     <row r="68">
@@ -4655,10 +4655,10 @@
         <v>1.5</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0697</v>
+        <v>1.0824</v>
       </c>
       <c r="J68" t="n">
-        <v>24.6031</v>
+        <v>24.8952</v>
       </c>
     </row>
     <row r="69">
@@ -4695,10 +4695,10 @@
         <v>1.42</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9497</v>
+        <v>0.9472</v>
       </c>
       <c r="J69" t="n">
-        <v>21.8431</v>
+        <v>21.7856</v>
       </c>
     </row>
     <row r="70">
@@ -4735,10 +4735,10 @@
         <v>1.22</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5593</v>
+        <v>0.5325</v>
       </c>
       <c r="J70" t="n">
-        <v>12.8639</v>
+        <v>12.2475</v>
       </c>
     </row>
     <row r="71">
@@ -4775,10 +4775,10 @@
         <v>1.17</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4476</v>
+        <v>0.417</v>
       </c>
       <c r="J71" t="n">
-        <v>10.2948</v>
+        <v>9.590999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -4815,10 +4815,10 @@
         <v>1.42</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7902</v>
+        <v>0.7397</v>
       </c>
       <c r="J72" t="n">
-        <v>19.755</v>
+        <v>18.4925</v>
       </c>
     </row>
     <row r="73">
@@ -4855,10 +4855,10 @@
         <v>1.28</v>
       </c>
       <c r="I73" t="n">
-        <v>0.573</v>
+        <v>0.5145</v>
       </c>
       <c r="J73" t="n">
-        <v>14.325</v>
+        <v>12.8625</v>
       </c>
     </row>
     <row r="74">
@@ -4895,10 +4895,10 @@
         <v>0.82</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.23</v>
+        <v>-0.2096</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.75</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="75">
@@ -4935,10 +4935,10 @@
         <v>0.76</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.289</v>
+        <v>-0.2704</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.225</v>
+        <v>-6.76</v>
       </c>
     </row>
     <row r="76">
@@ -4975,10 +4975,10 @@
         <v>0.59</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4438</v>
+        <v>-0.438</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.095</v>
+        <v>-10.95</v>
       </c>
     </row>
     <row r="77">
@@ -5015,10 +5015,10 @@
         <v>1.2</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5724</v>
+        <v>0.5327</v>
       </c>
       <c r="J77" t="n">
-        <v>14.31</v>
+        <v>13.3175</v>
       </c>
     </row>
     <row r="78">
@@ -5055,10 +5055,10 @@
         <v>1.12</v>
       </c>
       <c r="I78" t="n">
-        <v>0.382</v>
+        <v>0.3408</v>
       </c>
       <c r="J78" t="n">
-        <v>9.550000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="79">
@@ -5095,10 +5095,10 @@
         <v>1.03</v>
       </c>
       <c r="I79" t="n">
-        <v>0.129</v>
+        <v>0.1043</v>
       </c>
       <c r="J79" t="n">
-        <v>3.225</v>
+        <v>2.6075</v>
       </c>
     </row>
     <row r="80">
@@ -5135,10 +5135,10 @@
         <v>0.99</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0668</v>
+        <v>-0.0481</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.67</v>
+        <v>-1.2025</v>
       </c>
     </row>
     <row r="81">
@@ -5175,10 +5175,10 @@
         <v>0.92</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2978</v>
+        <v>-0.2567</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.445</v>
+        <v>-6.4175</v>
       </c>
     </row>
     <row r="82">
@@ -5215,10 +5215,10 @@
         <v>1.9</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6049</v>
+        <v>1.6484</v>
       </c>
       <c r="J82" t="n">
-        <v>40.1225</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="83">
@@ -5255,10 +5255,10 @@
         <v>1.24</v>
       </c>
       <c r="I83" t="n">
-        <v>0.6224</v>
+        <v>0.5935</v>
       </c>
       <c r="J83" t="n">
-        <v>15.56</v>
+        <v>14.8375</v>
       </c>
     </row>
     <row r="84">
@@ -5295,10 +5295,10 @@
         <v>1.19</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5151</v>
+        <v>0.4836</v>
       </c>
       <c r="J84" t="n">
-        <v>12.8775</v>
+        <v>12.09</v>
       </c>
     </row>
     <row r="85">
@@ -5335,10 +5335,10 @@
         <v>1.17</v>
       </c>
       <c r="I85" t="n">
-        <v>0.4699</v>
+        <v>0.4378</v>
       </c>
       <c r="J85" t="n">
-        <v>11.7475</v>
+        <v>10.945</v>
       </c>
     </row>
     <row r="86">
@@ -5375,10 +5375,10 @@
         <v>0.84</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5427</v>
+        <v>-0.5065</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.5675</v>
+        <v>-12.6625</v>
       </c>
     </row>
     <row r="87">
@@ -5415,10 +5415,10 @@
         <v>1.13</v>
       </c>
       <c r="I87" t="n">
-        <v>0.3747</v>
+        <v>0.3287</v>
       </c>
       <c r="J87" t="n">
-        <v>9.3675</v>
+        <v>8.217499999999999</v>
       </c>
     </row>
     <row r="88">
@@ -5455,10 +5455,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2237</v>
+        <v>-0.2069</v>
       </c>
       <c r="J88" t="n">
-        <v>-5.5925</v>
+        <v>-5.1725</v>
       </c>
     </row>
     <row r="89">
@@ -5495,10 +5495,10 @@
         <v>0.79</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2428</v>
+        <v>-0.2258</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.07</v>
+        <v>-5.645</v>
       </c>
     </row>
     <row r="90">
@@ -5535,10 +5535,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3895</v>
+        <v>-0.3772</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.737500000000001</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="91">
@@ -5575,10 +5575,10 @@
         <v>0.57</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4429</v>
+        <v>-0.4353</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.0725</v>
+        <v>-10.8825</v>
       </c>
     </row>
     <row r="92">
@@ -5615,10 +5615,10 @@
         <v>1.37</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9034</v>
+        <v>0.8859</v>
       </c>
       <c r="J92" t="n">
-        <v>26.1986</v>
+        <v>25.6911</v>
       </c>
     </row>
     <row r="93">
@@ -5655,10 +5655,10 @@
         <v>1.24</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6373</v>
+        <v>0.603</v>
       </c>
       <c r="J93" t="n">
-        <v>18.4817</v>
+        <v>17.487</v>
       </c>
     </row>
     <row r="94">
@@ -5695,10 +5695,10 @@
         <v>1.12</v>
       </c>
       <c r="I94" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J94" t="n">
-        <v>10.672</v>
+        <v>9.633800000000001</v>
       </c>
     </row>
     <row r="95">
@@ -5735,10 +5735,10 @@
         <v>1.12</v>
       </c>
       <c r="I95" t="n">
-        <v>0.368</v>
+        <v>0.3322</v>
       </c>
       <c r="J95" t="n">
-        <v>10.672</v>
+        <v>9.633800000000001</v>
       </c>
     </row>
     <row r="96">
@@ -5775,10 +5775,10 @@
         <v>0.92</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3173</v>
+        <v>-0.2763</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.201700000000001</v>
+        <v>-8.012700000000001</v>
       </c>
     </row>
     <row r="97">
@@ -5815,10 +5815,10 @@
         <v>1.46</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9032</v>
+        <v>0.8741</v>
       </c>
       <c r="J97" t="n">
-        <v>26.1928</v>
+        <v>25.3489</v>
       </c>
     </row>
     <row r="98">
@@ -5855,10 +5855,10 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0251</v>
+        <v>0.0195</v>
       </c>
       <c r="J98" t="n">
-        <v>0.7279</v>
+        <v>0.5655</v>
       </c>
     </row>
     <row r="99">
@@ -5895,10 +5895,10 @@
         <v>0.77</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2678</v>
+        <v>-0.2491</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.7662</v>
+        <v>-7.2239</v>
       </c>
     </row>
     <row r="100">
@@ -5935,10 +5935,10 @@
         <v>0.57</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4504</v>
+        <v>-0.4441</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.0616</v>
+        <v>-12.8789</v>
       </c>
     </row>
     <row r="101">
@@ -5975,10 +5975,10 @@
         <v>0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5282</v>
+        <v>-0.5319</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.3178</v>
+        <v>-15.4251</v>
       </c>
     </row>
     <row r="102">
@@ -6015,10 +6015,10 @@
         <v>1.53</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1212</v>
+        <v>1.1344</v>
       </c>
       <c r="J102" t="n">
-        <v>22.424</v>
+        <v>22.688</v>
       </c>
     </row>
     <row r="103">
@@ -6055,10 +6055,10 @@
         <v>1.31</v>
       </c>
       <c r="I103" t="n">
-        <v>0.756</v>
+        <v>0.7353</v>
       </c>
       <c r="J103" t="n">
-        <v>15.12</v>
+        <v>14.706</v>
       </c>
     </row>
     <row r="104">
@@ -6095,10 +6095,10 @@
         <v>1.28</v>
       </c>
       <c r="I104" t="n">
-        <v>0.697</v>
+        <v>0.6736</v>
       </c>
       <c r="J104" t="n">
-        <v>13.94</v>
+        <v>13.472</v>
       </c>
     </row>
     <row r="105">
@@ -6135,10 +6135,10 @@
         <v>1.28</v>
       </c>
       <c r="I105" t="n">
-        <v>0.697</v>
+        <v>0.6736</v>
       </c>
       <c r="J105" t="n">
-        <v>13.94</v>
+        <v>13.472</v>
       </c>
     </row>
     <row r="106">
@@ -6175,10 +6175,10 @@
         <v>1.23</v>
       </c>
       <c r="I106" t="n">
-        <v>0.5937</v>
+        <v>0.5662</v>
       </c>
       <c r="J106" t="n">
-        <v>11.874</v>
+        <v>11.324</v>
       </c>
     </row>
     <row r="107">
@@ -6215,10 +6215,10 @@
         <v>1.16</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4517</v>
+        <v>0.41</v>
       </c>
       <c r="J107" t="n">
-        <v>9.034000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="108">
@@ -6255,10 +6255,10 @@
         <v>0.85</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.1776</v>
+        <v>-0.162</v>
       </c>
       <c r="J108" t="n">
-        <v>-3.552</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="109">
@@ -6295,10 +6295,10 @@
         <v>0.74</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2857</v>
+        <v>-0.2699</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.714</v>
+        <v>-5.398</v>
       </c>
     </row>
     <row r="110">
@@ -6335,10 +6335,10 @@
         <v>0.5</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4999</v>
+        <v>-0.4984</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.997999999999999</v>
+        <v>-9.968</v>
       </c>
     </row>
     <row r="111">
@@ -6375,10 +6375,10 @@
         <v>0.49</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.5083</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.172</v>
+        <v>-10.166</v>
       </c>
     </row>
     <row r="112">
@@ -6415,10 +6415,10 @@
         <v>1.37</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9018</v>
+        <v>0.8842</v>
       </c>
       <c r="J112" t="n">
-        <v>26.1522</v>
+        <v>25.6418</v>
       </c>
     </row>
     <row r="113">
@@ -6455,10 +6455,10 @@
         <v>1.16</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4613</v>
+        <v>0.4246</v>
       </c>
       <c r="J113" t="n">
-        <v>13.3777</v>
+        <v>12.3134</v>
       </c>
     </row>
     <row r="114">
@@ -6495,10 +6495,10 @@
         <v>1.11</v>
       </c>
       <c r="I114" t="n">
-        <v>0.3422</v>
+        <v>0.3073</v>
       </c>
       <c r="J114" t="n">
-        <v>9.9238</v>
+        <v>8.9117</v>
       </c>
     </row>
     <row r="115">
@@ -6535,10 +6535,10 @@
         <v>1.11</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3422</v>
+        <v>0.3073</v>
       </c>
       <c r="J115" t="n">
-        <v>9.9238</v>
+        <v>8.9117</v>
       </c>
     </row>
     <row r="116">
@@ -6575,10 +6575,10 @@
         <v>1.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1763</v>
+        <v>0.1495</v>
       </c>
       <c r="J116" t="n">
-        <v>5.1127</v>
+        <v>4.3355</v>
       </c>
     </row>
     <row r="117">
@@ -6615,10 +6615,10 @@
         <v>1.26</v>
       </c>
       <c r="I117" t="n">
-        <v>0.5644</v>
+        <v>0.5092</v>
       </c>
       <c r="J117" t="n">
-        <v>16.3676</v>
+        <v>14.7668</v>
       </c>
     </row>
     <row r="118">
@@ -6655,10 +6655,10 @@
         <v>0.95</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J118" t="n">
-        <v>-2.2968</v>
+        <v>-1.9198</v>
       </c>
     </row>
     <row r="119">
@@ -6695,10 +6695,10 @@
         <v>0.93</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1047</v>
+        <v>-0.0896</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.0363</v>
+        <v>-2.5984</v>
       </c>
     </row>
     <row r="120">
@@ -6735,10 +6735,10 @@
         <v>0.77</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2722</v>
+        <v>-0.2531</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.8938</v>
+        <v>-7.3399</v>
       </c>
     </row>
     <row r="121">
@@ -6775,10 +6775,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4372</v>
+        <v>-0.4298</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.6788</v>
+        <v>-12.4642</v>
       </c>
     </row>
     <row r="122">
@@ -6815,10 +6815,10 @@
         <v>1.22</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4575</v>
+        <v>0.3993</v>
       </c>
       <c r="J122" t="n">
-        <v>13.725</v>
+        <v>11.979</v>
       </c>
     </row>
     <row r="123">
@@ -6855,10 +6855,10 @@
         <v>1.17</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3729</v>
+        <v>0.3182</v>
       </c>
       <c r="J123" t="n">
-        <v>11.187</v>
+        <v>9.545999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -6895,10 +6895,10 @@
         <v>1.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1645</v>
+        <v>0.1294</v>
       </c>
       <c r="J124" t="n">
-        <v>4.935</v>
+        <v>3.882</v>
       </c>
     </row>
     <row r="125">
@@ -6935,10 +6935,10 @@
         <v>1.04</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1203</v>
+        <v>0.092</v>
       </c>
       <c r="J125" t="n">
-        <v>3.609</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="126">
@@ -6975,10 +6975,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3237</v>
+        <v>-0.3075</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.711</v>
+        <v>-9.225</v>
       </c>
     </row>
     <row r="127">
@@ -7015,10 +7015,10 @@
         <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8515</v>
+        <v>0.8293</v>
       </c>
       <c r="J127" t="n">
-        <v>25.545</v>
+        <v>24.879</v>
       </c>
     </row>
     <row r="128">
@@ -7055,10 +7055,10 @@
         <v>1.07</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2494</v>
+        <v>0.214</v>
       </c>
       <c r="J128" t="n">
-        <v>7.482</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="129">
@@ -7095,10 +7095,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1282</v>
+        <v>0.1038</v>
       </c>
       <c r="J129" t="n">
-        <v>3.846</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="130">
@@ -7135,10 +7135,10 @@
         <v>1.03</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1282</v>
+        <v>0.1038</v>
       </c>
       <c r="J130" t="n">
-        <v>3.846</v>
+        <v>3.114</v>
       </c>
     </row>
     <row r="131">
@@ -7175,10 +7175,10 @@
         <v>0.83</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.529</v>
+        <v>-0.4879</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.87</v>
+        <v>-14.637</v>
       </c>
     </row>
     <row r="132">
@@ -7215,10 +7215,10 @@
         <v>1.65</v>
       </c>
       <c r="I132" t="n">
-        <v>1.3241</v>
+        <v>1.3482</v>
       </c>
       <c r="J132" t="n">
-        <v>31.7784</v>
+        <v>32.3568</v>
       </c>
     </row>
     <row r="133">
@@ -7255,10 +7255,10 @@
         <v>1.15</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4407</v>
+        <v>0.4029</v>
       </c>
       <c r="J133" t="n">
-        <v>10.5768</v>
+        <v>9.669600000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7295,10 +7295,10 @@
         <v>1</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0222</v>
+        <v>-0.0169</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.4056</v>
       </c>
     </row>
     <row r="135">
@@ -7335,10 +7335,10 @@
         <v>0.96</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1938</v>
+        <v>-0.1591</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.6512</v>
+        <v>-3.8184</v>
       </c>
     </row>
     <row r="136">
@@ -7375,10 +7375,10 @@
         <v>0.92</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3139</v>
+        <v>-0.2728</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.5336</v>
+        <v>-6.5472</v>
       </c>
     </row>
     <row r="137">
@@ -7415,10 +7415,10 @@
         <v>1.3</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6126</v>
+        <v>0.5558</v>
       </c>
       <c r="J137" t="n">
-        <v>14.7024</v>
+        <v>13.3392</v>
       </c>
     </row>
     <row r="138">
@@ -7455,10 +7455,10 @@
         <v>1.24</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5145</v>
+        <v>0.4565</v>
       </c>
       <c r="J138" t="n">
-        <v>12.348</v>
+        <v>10.956</v>
       </c>
     </row>
     <row r="139">
@@ -7495,10 +7495,10 @@
         <v>0.78</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2674</v>
+        <v>-0.248</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.4176</v>
+        <v>-5.952</v>
       </c>
     </row>
     <row r="140">
@@ -7535,10 +7535,10 @@
         <v>0.72</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3246</v>
+        <v>-0.3078</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.7904</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="141">
@@ -7575,10 +7575,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3339</v>
+        <v>-0.3177</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.0136</v>
+        <v>-7.6248</v>
       </c>
     </row>
     <row r="142">
@@ -7615,10 +7615,10 @@
         <v>1.5</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8948</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>26.844</v>
+        <v>25.479</v>
       </c>
     </row>
     <row r="143">
@@ -7655,10 +7655,10 @@
         <v>1.11</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2701</v>
+        <v>0.2221</v>
       </c>
       <c r="J143" t="n">
-        <v>8.103</v>
+        <v>6.663</v>
       </c>
     </row>
     <row r="144">
@@ -7695,10 +7695,10 @@
         <v>0.98</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0434</v>
+        <v>-0.0328</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.302</v>
+        <v>-0.984</v>
       </c>
     </row>
     <row r="145">
@@ -7735,10 +7735,10 @@
         <v>0.73</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3207</v>
+        <v>-0.3041</v>
       </c>
       <c r="J145" t="n">
-        <v>-9.621</v>
+        <v>-9.122999999999999</v>
       </c>
     </row>
     <row r="146">
@@ -7775,10 +7775,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3207</v>
+        <v>-0.3041</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.621</v>
+        <v>-9.122999999999999</v>
       </c>
     </row>
     <row r="147">
@@ -7815,10 +7815,10 @@
         <v>1.59</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2606</v>
+        <v>1.2827</v>
       </c>
       <c r="J147" t="n">
-        <v>37.818</v>
+        <v>38.481</v>
       </c>
     </row>
     <row r="148">
@@ -7855,10 +7855,10 @@
         <v>1.06</v>
       </c>
       <c r="I148" t="n">
-        <v>0.219</v>
+        <v>0.1868</v>
       </c>
       <c r="J148" t="n">
-        <v>6.57</v>
+        <v>5.604</v>
       </c>
     </row>
     <row r="149">
@@ -7895,10 +7895,10 @@
         <v>0.99</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.0718</v>
+        <v>-0.0521</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.154</v>
+        <v>-1.563</v>
       </c>
     </row>
     <row r="150">
@@ -7935,10 +7935,10 @@
         <v>0.97</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1496</v>
+        <v>-0.1188</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.488</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="151">
@@ -7975,10 +7975,10 @@
         <v>0.79</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6266</v>
+        <v>-0.5901</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.798</v>
+        <v>-17.703</v>
       </c>
     </row>
     <row r="152">
@@ -8015,10 +8015,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2391</v>
+        <v>1.2587</v>
       </c>
       <c r="J152" t="n">
-        <v>35.9339</v>
+        <v>36.5023</v>
       </c>
     </row>
     <row r="153">
@@ -8055,10 +8055,10 @@
         <v>1.19</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5376</v>
+        <v>0.4986</v>
       </c>
       <c r="J153" t="n">
-        <v>15.5904</v>
+        <v>14.4594</v>
       </c>
     </row>
     <row r="154">
@@ -8095,10 +8095,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1857</v>
+        <v>0.1571</v>
       </c>
       <c r="J154" t="n">
-        <v>5.3853</v>
+        <v>4.5559</v>
       </c>
     </row>
     <row r="155">
@@ -8135,10 +8135,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3355</v>
+        <v>-0.2935</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.7295</v>
+        <v>-8.5115</v>
       </c>
     </row>
     <row r="156">
@@ -8175,10 +8175,10 @@
         <v>0.79</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6312</v>
+        <v>-0.5954</v>
       </c>
       <c r="J156" t="n">
-        <v>-18.3048</v>
+        <v>-17.2666</v>
       </c>
     </row>
     <row r="157">
@@ -8215,10 +8215,10 @@
         <v>1.41</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7617</v>
+        <v>0.7075</v>
       </c>
       <c r="J157" t="n">
-        <v>22.0893</v>
+        <v>20.5175</v>
       </c>
     </row>
     <row r="158">
@@ -8255,10 +8255,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6558</v>
+        <v>0.5976</v>
       </c>
       <c r="J158" t="n">
-        <v>19.0182</v>
+        <v>17.3304</v>
       </c>
     </row>
     <row r="159">
@@ -8295,10 +8295,10 @@
         <v>1.03</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0984</v>
+        <v>0.073</v>
       </c>
       <c r="J159" t="n">
-        <v>2.8536</v>
+        <v>2.117</v>
       </c>
     </row>
     <row r="160">
@@ -8335,10 +8335,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2437</v>
+        <v>-0.2236</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.0673</v>
+        <v>-6.4844</v>
       </c>
     </row>
     <row r="161">
@@ -8375,10 +8375,10 @@
         <v>0.48</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5407</v>
+        <v>-0.5485</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.6803</v>
+        <v>-15.9065</v>
       </c>
     </row>
     <row r="162">
@@ -8415,10 +8415,10 @@
         <v>1.22</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4642</v>
+        <v>0.4057</v>
       </c>
       <c r="J162" t="n">
-        <v>13.926</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="163">
@@ -8455,10 +8455,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3788</v>
+        <v>0.3235</v>
       </c>
       <c r="J163" t="n">
-        <v>11.364</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="164">
@@ -8495,10 +8495,10 @@
         <v>1.14</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3253</v>
+        <v>0.2731</v>
       </c>
       <c r="J164" t="n">
-        <v>9.759</v>
+        <v>8.193</v>
       </c>
     </row>
     <row r="165">
@@ -8535,10 +8535,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2537</v>
+        <v>-0.2339</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.611</v>
+        <v>-7.017</v>
       </c>
     </row>
     <row r="166">
@@ -8575,10 +8575,10 @@
         <v>0.74</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3117</v>
+        <v>-0.2945</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.351000000000001</v>
+        <v>-8.835000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -8615,10 +8615,10 @@
         <v>1.34</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6344</v>
+        <v>0.5748</v>
       </c>
       <c r="J167" t="n">
-        <v>19.032</v>
+        <v>17.244</v>
       </c>
     </row>
     <row r="168">
@@ -8655,10 +8655,10 @@
         <v>1.31</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5889</v>
+        <v>0.5291</v>
       </c>
       <c r="J168" t="n">
-        <v>17.667</v>
+        <v>15.873</v>
       </c>
     </row>
     <row r="169">
@@ -8695,10 +8695,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2012</v>
+        <v>0.1632</v>
       </c>
       <c r="J169" t="n">
-        <v>6.036</v>
+        <v>4.896</v>
       </c>
     </row>
     <row r="170">
@@ -8735,10 +8735,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.05</v>
+        <v>-0.0381</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.5</v>
+        <v>-1.143</v>
       </c>
     </row>
     <row r="171">
@@ -8775,10 +8775,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2805</v>
+        <v>-0.2623</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.414999999999999</v>
+        <v>-7.869</v>
       </c>
     </row>
   </sheetData>
